--- a/excel/03_Modelo_Financiero_Embudo_de_Llamada.xlsx
+++ b/excel/03_Modelo_Financiero_Embudo_de_Llamada.xlsx
@@ -170,8 +170,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -974,7 +974,7 @@
           <t>&lt;1,5</t>
         </is>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="19">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
@@ -1190,7 +1190,7 @@
           <t>&gt;1,5 %</t>
         </is>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="18">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
@@ -1226,7 +1226,7 @@
           <t>&lt;60</t>
         </is>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <f>'Modelo'!$C$20</f>
         <v/>
       </c>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C7" s="36">
-        <f>IF(ISERROR(SUM('Embudo'!C5:I60)),"REVISAR","OK")</f>
+        <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2907,7 +2907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J25"/>
+  <dimension ref="B2:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2915,24 +2915,23 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Embudo: todos los pasos, cuántos, qué porcentaje pasa y cuánto cuesta cada uno</t>
+          <t>Embudo: todos los pasos, cuántos pasan y, por cada uno, qué pagás, qué te queda y hasta cuánto podrías pagar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). El costo por paso es inversión ÷ cantidad; el techo por paso es lo máximo que podrías pagar por él si lo demás se mantiene. Los pasos sin costo propio ya se pagaron con el CPA: mejoran el AOV.</t>
+          <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). Tres números por paso: lo que pagás hoy por cada uno (inversión ÷ cantidad), lo que te queda por cada uno (ganancia ÷ cantidad) y lo máximo que podrías pagar (el techo: lo que cada uno genera en cash neto). Techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
@@ -2954,30 +2953,25 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>% que se pierde</t>
+          <t>% acumulado</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>% acumulado</t>
+          <t>Costo por paso (pagás hoy)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Costo por paso</t>
+          <t>Ganancia por paso (te queda)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Techo por paso</t>
+          <t>Techo por paso (máximo a pagar)</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Ganancia por paso</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Qué se paga acá / cómo se lee</t>
         </is>
@@ -2986,7 +2980,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Impresiones del anuncio</t>
+          <t>Impresiones del anuncio (por mil)</t>
         </is>
       </c>
       <c r="C6" s="16">
@@ -3003,27 +2997,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F6" s="12">
+        <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8*1000/'Modelo'!$C$7)</f>
+        <v/>
       </c>
       <c r="G6" s="12">
-        <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8*1000/'Modelo'!$C$7)</f>
-        <v/>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="12">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$40*1000/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Costo por mil impresiones (CPM).</t>
+      <c r="H6" s="12">
+        <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1000/'Modelo'!$C$7)</f>
+        <v/>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Costo por mil impresiones (CPM) y CPM máximo.</t>
         </is>
       </c>
     </row>
@@ -3041,28 +3029,24 @@
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$8/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="E7" s="17">
-        <f>IF('Modelo'!$C$7=0,0,1-'Modelo'!$C$8/'Modelo'!$C$7)</f>
-        <v/>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="F7" s="12">
+        <f>IF('Modelo'!$C$8=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$8)</f>
+        <v/>
+      </c>
       <c r="G7" s="12">
-        <f>IF('Modelo'!$C$8=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$8)</f>
-        <v/>
-      </c>
-      <c r="H7" s="18">
+        <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$40*1/'Modelo'!$C$8)</f>
+        <v/>
+      </c>
+      <c r="H7" s="12">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="I7" s="12">
-        <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$40*1/'Modelo'!$C$8)</f>
-        <v/>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Costo por clic (CTR).</t>
         </is>
@@ -3082,28 +3066,24 @@
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="17">
-        <f>IF('Modelo'!$C$8=0,0,1-'Modelo'!$C$9/'Modelo'!$C$8)</f>
-        <v/>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="F8" s="12">
+        <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
+        <v/>
+      </c>
       <c r="G8" s="12">
-        <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="H8" s="18">
+        <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$40*1/'Modelo'!$C$9)</f>
+        <v/>
+      </c>
+      <c r="H8" s="12">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="I8" s="12">
-        <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$40*1/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Costo por visita.</t>
         </is>
@@ -3123,27 +3103,23 @@
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E9" s="17">
-        <f>IF('Modelo'!$C$9=0,0,1-'Modelo'!$C$11/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="19">
+      <c r="E9" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$11/'Modelo'!$C$11)</f>
         <v/>
       </c>
+      <c r="F9" s="12">
+        <f>IF('Modelo'!$C$11=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$11)</f>
+        <v/>
+      </c>
       <c r="G9" s="12">
-        <f>IF('Modelo'!$C$11=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$11)</f>
-        <v/>
-      </c>
-      <c r="H9" s="18">
+        <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$40*1/'Modelo'!$C$11)</f>
+        <v/>
+      </c>
+      <c r="H9" s="12">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="I9" s="12">
-        <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$40*1/'Modelo'!$C$11)</f>
-        <v/>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>CPL real.</t>
         </is>
@@ -3163,27 +3139,23 @@
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$13/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="E10" s="17">
-        <f>IF('Modelo'!$C$11=0,0,1-'Modelo'!$C$13/'Modelo'!$C$11)</f>
-        <v/>
-      </c>
-      <c r="F10" s="19">
+      <c r="E10" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$13/'Modelo'!$C$11)</f>
         <v/>
       </c>
+      <c r="F10" s="12">
+        <f>IF('Modelo'!$C$13=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$13)</f>
+        <v/>
+      </c>
       <c r="G10" s="12">
-        <f>IF('Modelo'!$C$13=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$13)</f>
-        <v/>
-      </c>
-      <c r="H10" s="18">
+        <f>IF('Modelo'!$C$13=0,0,'Modelo'!$C$40*1/'Modelo'!$C$13)</f>
+        <v/>
+      </c>
+      <c r="H10" s="12">
         <f>IF('Modelo'!$C$13=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$13)</f>
         <v/>
       </c>
-      <c r="I10" s="12">
-        <f>IF('Modelo'!$C$13=0,0,'Modelo'!$C$40*1/'Modelo'!$C$13)</f>
-        <v/>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Solo cuenta con el interruptor de evento en 1; si no, queda en 0.</t>
         </is>
@@ -3203,27 +3175,23 @@
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$15/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="E11" s="17">
-        <f>IF('Modelo'!$C$11=0,0,1-'Modelo'!$C$15/'Modelo'!$C$11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="19">
+      <c r="E11" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$15/'Modelo'!$C$11)</f>
         <v/>
       </c>
+      <c r="F11" s="12">
+        <f>IF('Modelo'!$C$15=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$15)</f>
+        <v/>
+      </c>
       <c r="G11" s="12">
-        <f>IF('Modelo'!$C$15=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$15)</f>
-        <v/>
-      </c>
-      <c r="H11" s="18">
+        <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$40*1/'Modelo'!$C$15)</f>
+        <v/>
+      </c>
+      <c r="H11" s="12">
         <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="I11" s="12">
-        <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$40*1/'Modelo'!$C$15)</f>
-        <v/>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Costo por aplicación. Sobre leads (sobre asistentes si hay evento).</t>
         </is>
@@ -3243,27 +3211,23 @@
         <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$16/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="E12" s="17">
-        <f>IF('Modelo'!$C$15=0,0,1-'Modelo'!$C$16/'Modelo'!$C$15)</f>
-        <v/>
-      </c>
-      <c r="F12" s="19">
+      <c r="E12" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$16/'Modelo'!$C$11)</f>
         <v/>
       </c>
+      <c r="F12" s="12">
+        <f>IF('Modelo'!$C$16=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$16)</f>
+        <v/>
+      </c>
       <c r="G12" s="12">
-        <f>IF('Modelo'!$C$16=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$16)</f>
-        <v/>
-      </c>
-      <c r="H12" s="18">
+        <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$40*1/'Modelo'!$C$16)</f>
+        <v/>
+      </c>
+      <c r="H12" s="12">
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="I12" s="12">
-        <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$40*1/'Modelo'!$C$16)</f>
-        <v/>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Sobre aplicaciones. Palanca: las preguntas del formulario.</t>
         </is>
@@ -3283,27 +3247,23 @@
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$17/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="E13" s="17">
-        <f>IF('Modelo'!$C$16=0,0,1-'Modelo'!$C$17/'Modelo'!$C$16)</f>
-        <v/>
-      </c>
-      <c r="F13" s="19">
+      <c r="E13" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$17/'Modelo'!$C$11)</f>
         <v/>
       </c>
+      <c r="F13" s="12">
+        <f>IF('Modelo'!$C$17=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$17)</f>
+        <v/>
+      </c>
       <c r="G13" s="12">
-        <f>IF('Modelo'!$C$17=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$17)</f>
-        <v/>
-      </c>
-      <c r="H13" s="18">
+        <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$40*1/'Modelo'!$C$17)</f>
+        <v/>
+      </c>
+      <c r="H13" s="12">
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="I13" s="12">
-        <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$40*1/'Modelo'!$C$17)</f>
-        <v/>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Costo por agenda. Sobre calificados. Palancas: setter, confirmación por WhatsApp.</t>
         </is>
@@ -3323,27 +3283,23 @@
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$18/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="E14" s="17">
-        <f>IF('Modelo'!$C$17=0,0,1-'Modelo'!$C$18/'Modelo'!$C$17)</f>
-        <v/>
-      </c>
-      <c r="F14" s="19">
+      <c r="E14" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$18/'Modelo'!$C$11)</f>
         <v/>
       </c>
+      <c r="F14" s="12">
+        <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$18)</f>
+        <v/>
+      </c>
       <c r="G14" s="12">
-        <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$18)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18">
+        <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$40*1/'Modelo'!$C$18)</f>
+        <v/>
+      </c>
+      <c r="H14" s="12">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="I14" s="12">
-        <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$40*1/'Modelo'!$C$18)</f>
-        <v/>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Costo por llamada realizada. Sobre agendas. Palancas: recordatorio, video de bienvenida.</t>
         </is>
@@ -3363,27 +3319,23 @@
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$23/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
-        <f>IF('Modelo'!$C$18=0,0,1-'Modelo'!$C$23/'Modelo'!$C$18)</f>
-        <v/>
-      </c>
-      <c r="F15" s="19">
+      <c r="E15" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
+      <c r="F15" s="12">
+        <f>IF('Modelo'!$C$23=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$23)</f>
+        <v/>
+      </c>
       <c r="G15" s="12">
-        <f>IF('Modelo'!$C$23=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$23)</f>
-        <v/>
-      </c>
-      <c r="H15" s="18">
+        <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$40*1/'Modelo'!$C$23)</f>
+        <v/>
+      </c>
+      <c r="H15" s="12">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="I15" s="12">
-        <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$40*1/'Modelo'!$C$23)</f>
-        <v/>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>CAC. Sobre llamadas (cierre). Juzgar con 3 a 4 eventos, nunca con uno.</t>
         </is>
@@ -3403,17 +3355,18 @@
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$24/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="E16" s="17">
-        <f>IF('Modelo'!$C$18=0,0,1-'Modelo'!$C$24/'Modelo'!$C$18)</f>
-        <v/>
-      </c>
-      <c r="F16" s="19">
+      <c r="E16" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$24/'Modelo'!$C$11)</f>
         <v/>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3421,12 +3374,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Sobre llamadas que no compraron. Se pagó con el CAC; suma al facturado.</t>
         </is>
@@ -3435,53 +3383,70 @@
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>Comprobalo con la fila de la unidad: costo + ganancia + fijos repartidos = techo</t>
+        </is>
+      </c>
+      <c r="F18" s="19">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="H18" s="12">
+        <f>F9+G9+'Supuestos'!$C$37/'Modelo'!$C$11</f>
+        <v/>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Techo = costo + ganancia + fijos ÷ unidades. Lo que falta entre (costo + ganancia) y el techo son los costos fijos repartidos entre las unidades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Cómo se lee</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Cantidad: cuántas acciones o personas hubo en ese paso con los supuestos del escenario en uso.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % que se pierde es el complemento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>% acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
+          <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Costo por paso: inversión ÷ cantidad. Es lo que te está costando hoy cada persona que llega a ese paso.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
+    <row r="23" ht="28" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Techo por paso: lo máximo que podrías pagar por ese paso sin perder plata, si lo demás se mantiene. Comparalo con el costo por paso: si el costo está por encima del techo, ese paso está caro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
+          <t>Ganancia por paso: ganancia del período ÷ cantidad. Lo que te queda por cada persona de ese paso después de pagar la pauta, las comisiones, los reembolsos y los fijos. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Ganancia por paso: la ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo: cuánto te queda por cada visita, por cada lead, por cada comprador. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
+          <t>Techo por paso: lo que cada persona de ese paso genera en cash neto (cash neto menos costos por unidad, dividido por la cantidad). Es lo máximo que podrías pagar por ese paso antes de que la ganancia llegue a cero, si lo demás se mantiene. Por eso siempre es mayor que la ganancia: techo = costo + ganancia + fijos repartidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Los bumps, las OTOs y la ascensión no tienen costo propio: se pagan con el CPA del comprador principal y se miden por lo que suman al AOV.</t>
@@ -3489,14 +3454,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B20:J20"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B21:J21"/>
+  <mergeCells count="6">
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -3639,7 +3603,7 @@
           <t>CPM (costo por mil impresiones)</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>IF('Supuestos'!$C$6=1,D9,IF('Supuestos'!$C$6=2,E9,F9))</f>
         <v/>
       </c>
@@ -4611,7 +4575,7 @@
           <t>Costo por aplicación</t>
         </is>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="19">
         <f>IF('Modelo'!$C$15=0,0,'Supuestos'!$C$8/'Modelo'!$C$15)</f>
         <v/>
       </c>
@@ -4643,7 +4607,7 @@
           <t>Costo por llamada realizada</t>
         </is>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8/'Modelo'!$C$18)</f>
         <v/>
       </c>
@@ -4700,7 +4664,7 @@
           <t>% de leads que compran el programa</t>
         </is>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -4780,7 +4744,7 @@
           <t>Facturado por comprador del programa</t>
         </is>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="19">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$29/'Modelo'!$C$23)</f>
         <v/>
       </c>
@@ -4796,7 +4760,7 @@
           <t>Ventas del programa por lead (para la proyección)</t>
         </is>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -4812,7 +4776,7 @@
           <t>Facturado por lead</t>
         </is>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$29/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -5086,7 +5050,7 @@
           <t>Techo de costo por aplicación</t>
         </is>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="19">
         <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$47*'Modelo'!$C$11/'Modelo'!$C$15)</f>
         <v/>
       </c>
@@ -5118,7 +5082,7 @@
           <t>Techo de costo por llamada realizada</t>
         </is>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="19">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$47*'Modelo'!$C$11/'Modelo'!$C$18)</f>
         <v/>
       </c>
@@ -5134,7 +5098,7 @@
           <t>Techo de costo por venta (CAC máximo)</t>
         </is>
       </c>
-      <c r="C53" s="18">
+      <c r="C53" s="19">
         <f>IF('Modelo'!$C$25=0,0,'Modelo'!$C$47/'Modelo'!$C$25)</f>
         <v/>
       </c>
@@ -5150,7 +5114,7 @@
           <t>Objetivo de CAC</t>
         </is>
       </c>
-      <c r="C54" s="18">
+      <c r="C54" s="19">
         <f>'Modelo'!$C$53/(1+'Supuestos'!$C$46)</f>
         <v/>
       </c>
@@ -5280,7 +5244,7 @@
           <t>Ganancia por clic</t>
         </is>
       </c>
-      <c r="C63" s="18">
+      <c r="C63" s="19">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$40/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -5312,7 +5276,7 @@
           <t>Ganancia por agenda</t>
         </is>
       </c>
-      <c r="C65" s="18">
+      <c r="C65" s="19">
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$40/'Modelo'!$C$17)</f>
         <v/>
       </c>
@@ -5328,7 +5292,7 @@
           <t>Ganancia por llamada</t>
         </is>
       </c>
-      <c r="C66" s="18">
+      <c r="C66" s="19">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$40/'Modelo'!$C$18)</f>
         <v/>
       </c>
@@ -6128,23 +6092,23 @@
           <t>Costo máximo (facturado por unidad ÷ ROAS)</t>
         </is>
       </c>
-      <c r="C47" s="18">
+      <c r="C47" s="19">
         <f>IF(C46=0,0,'Modelo'!$C$32/C46)</f>
         <v/>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="19">
         <f>IF(D46=0,0,'Modelo'!$C$32/D46)</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="19">
         <f>IF(E46=0,0,'Modelo'!$C$32/E46)</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="19">
         <f>IF(F46=0,0,'Modelo'!$C$32/F46)</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="19">
         <f>IF(G46=0,0,'Modelo'!$C$32/G46)</f>
         <v/>
       </c>
@@ -8033,15 +7997,15 @@
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N8=0,0,N7/N8))</f>
         <v/>
       </c>
-      <c r="O18" s="18">
+      <c r="O18" s="19">
         <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
         <v/>
       </c>
-      <c r="P18" s="18">
+      <c r="P18" s="19">
         <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
         <v/>
       </c>
-      <c r="Q18" s="18">
+      <c r="Q18" s="19">
         <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
         <v/>
       </c>
@@ -8320,63 +8284,63 @@
           <t>Costo por agenda</t>
         </is>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="19">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C11=0,0,C7/C11))</f>
         <v/>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="19">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D11=0,0,D7/D11))</f>
         <v/>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="19">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E11=0,0,E7/E11))</f>
         <v/>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F11=0,0,F7/F11))</f>
         <v/>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="19">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G11=0,0,G7/G11))</f>
         <v/>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="19">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H11=0,0,H7/H11))</f>
         <v/>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="19">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I11=0,0,I7/I11))</f>
         <v/>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="19">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J11=0,0,J7/J11))</f>
         <v/>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="19">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K11=0,0,K7/K11))</f>
         <v/>
       </c>
-      <c r="L23" s="18">
+      <c r="L23" s="19">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L11=0,0,L7/L11))</f>
         <v/>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="19">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M11=0,0,M7/M11))</f>
         <v/>
       </c>
-      <c r="N23" s="18">
+      <c r="N23" s="19">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N11=0,0,N7/N11))</f>
         <v/>
       </c>
-      <c r="O23" s="18">
+      <c r="O23" s="19">
         <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
         <v/>
       </c>
-      <c r="P23" s="18">
+      <c r="P23" s="19">
         <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
         <v/>
       </c>
-      <c r="Q23" s="18">
+      <c r="Q23" s="19">
         <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
         <v/>
       </c>
@@ -8387,63 +8351,63 @@
           <t>CAC real</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="19">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C13=0,0,C7/C13))</f>
         <v/>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="19">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D13=0,0,D7/D13))</f>
         <v/>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="19">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E13=0,0,E7/E13))</f>
         <v/>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="19">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F13=0,0,F7/F13))</f>
         <v/>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="19">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G13=0,0,G7/G13))</f>
         <v/>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="19">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H13=0,0,H7/H13))</f>
         <v/>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="19">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I13=0,0,I7/I13))</f>
         <v/>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="19">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J13=0,0,J7/J13))</f>
         <v/>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="19">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K13=0,0,K7/K13))</f>
         <v/>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="19">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L13=0,0,L7/L13))</f>
         <v/>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="19">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M13=0,0,M7/M13))</f>
         <v/>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="19">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N13=0,0,N7/N13))</f>
         <v/>
       </c>
-      <c r="O24" s="18">
+      <c r="O24" s="19">
         <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
         <v/>
       </c>
-      <c r="P24" s="18">
+      <c r="P24" s="19">
         <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
         <v/>
       </c>
-      <c r="Q24" s="18">
+      <c r="Q24" s="19">
         <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
         <v/>
       </c>
@@ -8502,15 +8466,15 @@
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N8=0,0,(N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36)/N8))</f>
         <v/>
       </c>
-      <c r="O25" s="18">
+      <c r="O25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
         <v/>
       </c>
-      <c r="P25" s="18">
+      <c r="P25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
         <v/>
       </c>
-      <c r="Q25" s="18">
+      <c r="Q25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
         <v/>
       </c>
@@ -8703,15 +8667,15 @@
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N8=0,0,(N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)/N8))</f>
         <v/>
       </c>
-      <c r="O28" s="18">
+      <c r="O28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
         <v/>
       </c>
-      <c r="P28" s="18">
+      <c r="P28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
         <v/>
       </c>
-      <c r="Q28" s="18">
+      <c r="Q28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
         <v/>
       </c>
@@ -8856,63 +8820,63 @@
           <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
         </is>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="19">
         <f>IF(COUNT(C7:C16)&lt;10,"",'Modelo'!$C$48)</f>
         <v/>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="19">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(COUNT(C25:C25)&gt;0,MEDIAN(C25:C25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="19">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(COUNT(C25:D25)&gt;0,MEDIAN(C25:D25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="19">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(COUNT(C25:E25)&gt;0,MEDIAN(C25:E25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="19">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(COUNT(C25:F25)&gt;0,MEDIAN(C25:F25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="19">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(COUNT(D25:G25)&gt;0,MEDIAN(D25:G25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="19">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(COUNT(E25:H25)&gt;0,MEDIAN(E25:H25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="J31" s="18">
+      <c r="J31" s="19">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(COUNT(F25:I25)&gt;0,MEDIAN(F25:I25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="K31" s="18">
+      <c r="K31" s="19">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(COUNT(G25:J25)&gt;0,MEDIAN(G25:J25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="L31" s="18">
+      <c r="L31" s="19">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(COUNT(H25:K25)&gt;0,MEDIAN(H25:K25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="M31" s="18">
+      <c r="M31" s="19">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(COUNT(I25:L25)&gt;0,MEDIAN(I25:L25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="N31" s="18">
+      <c r="N31" s="19">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(COUNT(J25:M25)&gt;0,MEDIAN(J25:M25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="O31" s="18">
+      <c r="O31" s="19">
         <f>IF(COUNT(C31:N31)=0,"",AVERAGE(C31:N31))</f>
         <v/>
       </c>
-      <c r="P31" s="18">
+      <c r="P31" s="19">
         <f>IF(COUNT(C31:N31)=0,"",MAX(C31:N31))</f>
         <v/>
       </c>
-      <c r="Q31" s="18">
+      <c r="Q31" s="19">
         <f>IF(COUNT(C31:N31)=0,"",MIN(C31:N31))</f>
         <v/>
       </c>

--- a/excel/03_Modelo_Financiero_Embudo_de_Llamada.xlsx
+++ b/excel/03_Modelo_Financiero_Embudo_de_Llamada.xlsx
@@ -19,8 +19,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chequeos" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencia" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="Autor_Jesus_Tassarolo">"Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro"</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -34,7 +37,7 @@
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +59,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="008C8C8C"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="6">
@@ -145,8 +153,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -578,288 +587,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B48"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Modelo financiero · Embudo de llamada (high ticket)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Anuncios → página con VSL (o webinar previo) → aplicación → agenda → llamada → cierre → cash en cuotas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Para qué sirve este modelo</t>
         </is>
       </c>
     </row>
     <row r="6" ht="75" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Es el modelo financiero de un embudo de llamada: anuncios que captan leads, una página con video o un webinar que los lleva a aplicar, una agenda, una llamada con un closer y una venta de ticket alto que se cobra al contado o en cuotas. Con tus números (o con el ejemplo cargado) te dice cuánto vale cada lead que comprás con publicidad, hasta cuánto podés pagar por lead y por cada etapa siguiente, cuánto invertir para una meta de ventas, cuánta caja necesitás y qué palanca mejora más la ganancia.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>La unidad que comprás es el lead. El número que manda es el costo por agenda contra lo que vale una agenda, y después el cierre. Con ticket alto una venta más o menos cambia el ROAS de un mes: juzgá por ventanas de 3 a 4 eventos, nunca por uno.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Cómo usarlo en 6 pasos</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>1. Andá a Supuestos y reemplazá el ejemplo por tus números. Si todavía no tenés datos, dejá el escenario en 1 (conservador) y usá Benchmarks como referencia.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>2. Mirá Resumen: ganancia del mes, ROAS, el techo y el objetivo de costo por lead, y el semáforo. Después Embudo: todos los pasos en orden con cuántos pasan, qué porcentaje se pierde y cuánto cuesta cada paso.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>3. Abrí Escenarios para ver qué pasa si cambia el precio, la conversión o el costo. Las celdas amarillas de cada tabla se pueden cambiar.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>4. Abrí Sensibilidad para saber qué variable conviene trabajar primero.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>5. Antes de invertir, mirá Proyección 12 meses: la caja necesaria es la plata que tenés que tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>6. Cuando el embudo esté andando, completá una columna de Seguimiento por mes. El semáforo te dice si estás pagando de más por cada lead.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Colores y hojas</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Amarillo = celda que editás vos. Azul = resultado calculado: no lo toques, se recalcula solo.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Resumen, Embudo y Modelo leen de Supuestos. Escenarios y Sensibilidad recalculan el modelo entero cambiando una o dos variables. Proyección usa los mismos supuestos mes a mes. Seguimiento es la única hoja, además de Supuestos, donde cargás datos.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Chequeos avisa si un supuesto quedó fuera de rango. Si dice REVISAR, arreglalo antes de leer los resultados.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Cómo elegir escenario: en Supuestos, la celda 'Escenario en uso' (1, 2 o 3) elige la columna conservador, base u optimista de cada fila que tiene tres valores. Las filas con un solo valor se usan tal cual.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>El ejemplo que viene cargado</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Un programa de 1.500 USD vendido por llamada. Se invierten 4.500 USD por mes a CPM 10 y CTR 1,5 %; el 85 % de los clics carga la página y el 28 % deja sus datos: CPL cerca de 2,80 y unos 1.600 leads.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Sin evento previo (interruptor en 0): el 10 % de los leads completa la aplicación, el 60 % califica, el 60 % de los calificados agenda, el 70 % aparece en la llamada y el 25 % compra: unas 10 ventas por mes. A los que no compran se les ofrece un downsell de 497 que toma el 10 %.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Si tenés un webinar antes de la aplicación, poné el interruptor en 1 y el % de asistencia: la aplicación pasa a medirse sobre asistentes.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Costos: pasarela 5 %, closers 10 % del cash cobrado, reembolsos 5 %, 0,20 por lead en WhatsApp y setter, fijos 2.500 por mes. Cobranza 60 / 20 / 20: el facturado se cobra en tres meses.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Resultado: facturado cerca de 17.000 por mes y ROAS sobre cash neto de 3 con la cobranza completa, pero solo 1,8 con lo que entra el primer mes. En este ejemplo el embudo se autofinancia (la caja necesaria da 0): subí el crecimiento mensual o bajá la cobranza del mes 1 en Supuestos y vas a ver en qué mes la caja empieza a hacer falta. El techo de CPL queda cerca de 8: el tráfico no es el cuello de botella, el cierre sí.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Reglas de decisión (el protocolo corto)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>1. Antes de invertir: cargá tus números en Supuestos (si no tenés datos, escenario 1, conservador) y mirá en Resumen el techo y el objetivo de costo por lead.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>2. Primeros días: compará tu costo real por lead con el objetivo. Verde: seguí. Amarillo: no subas la inversión y revisá en este orden: CPM (público y frecuencia), creativo (CTR) y página (conversión). Rojo: bajá un escalón (−25 %) y arreglá antes de volver a subir.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>3. Cada mes: completá una columna de Seguimiento. El semáforo compara tu costo con el techo móvil (lo que rindieron tus últimas 4 columnas), no con un número fijo.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>4. Subí la inversión de a 25 % y esperá 7 días (o 3 a 4 eventos si vendés por llamada) antes de volver a subir. Un día bueno o malo no decide nada.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>5. Si el costo está en verde y aun así no hay ganancia, el problema no es el tráfico: mirá asistencia, conversión de la oferta y cobranza, en ese orden.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>6. Cambiá una sola cosa por vez. Si cambiás precio, creativo y página la misma semana no vas a saber qué funcionó.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>7. Trabajá siempre con cash neto (lo que entra menos comisiones y reembolsos), nunca con facturado. En Proyección ves cuánta caja necesitás para sostener la pauta mientras cobrás.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>8. En llamada, el techo de CPL casi nunca es el problema: lo que mata el mes es un cierre bajo o un show de llamadas bajo. Mirá primero % de agenda, show de la llamada y cierre; el CPL al final.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>9. Facturado no es cash. Con cuotas, el ROAS sobre facturado puede dar 3 mientras la caja del mes queda en rojo. Decidí con cash neto y mirá la caja mínima de Proyección.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Lo que este modelo no hace</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>No adivina tus conversiones: usa las que cargás. Cuando una conversión cambia, el techo cambia; por eso Seguimiento recalcula el techo móvil con tus últimas 4 columnas.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>No reemplaza la decisión: la informa. Las reglas de arriba dicen qué hacer con cada color.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Los benchmarks son orden de magnitud para tráfico frío en español. Tus datos mandan.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Autor y versión</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro. v1.2 · octubre 2026. Fórmulas compatibles con Excel, Google Sheets y Numbers. Sin macros.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Este modelo se comparte para que lo uses con tus números. Si lo compartís, dejá esta línea: es la forma de saber de dónde salió.</t>
         </is>
@@ -868,10 +884,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -884,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -897,52 +913,59 @@
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Benchmarks: contra qué comparar tus números</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Valores de referencia para tráfico frío en español. Son orden de magnitud, no objetivo: tus propios datos de Seguimiento mandan.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Malo</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Bueno</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Ganador</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Tu valor (Modelo)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Fuente / nota</t>
         </is>
@@ -974,11 +997,11 @@
           <t>&lt;1,5</t>
         </is>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Hispano, ticket 500 a 3.000, 2024 a 2026.</t>
         </is>
@@ -1010,11 +1033,11 @@
           <t>&gt;18 %</t>
         </is>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="18">
         <f>'Supuestos'!$C$21</f>
         <v/>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Formulario largo. Con evento previo se mide sobre asistentes.</t>
         </is>
@@ -1046,11 +1069,11 @@
           <t>&gt;70 %</t>
         </is>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="18">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Depende de la dureza del filtro.</t>
         </is>
@@ -1082,11 +1105,11 @@
           <t>&gt;70 %</t>
         </is>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="18">
         <f>'Supuestos'!$C$23</f>
         <v/>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Mercado: 30 a 60 % de las aplicaciones terminan agendadas.</t>
         </is>
@@ -1118,11 +1141,11 @@
           <t>&gt;75 %</t>
         </is>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="18">
         <f>'Supuestos'!$C$24</f>
         <v/>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Mercado: no-show del 20 a 30 %; equipos muy buenos, 8 a 12 %.</t>
         </is>
@@ -1154,11 +1177,11 @@
           <t>&gt;35 %</t>
         </is>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="18">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Lead tibio y filtrado: promedio 30 %. Sin filtro: menos de 5 %. Sin consenso por ticket.</t>
         </is>
@@ -1190,11 +1213,11 @@
           <t>&gt;1,5 %</t>
         </is>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>El producto de todas las conversiones.</t>
         </is>
@@ -1226,11 +1249,11 @@
           <t>&lt;60</t>
         </is>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="20">
         <f>'Modelo'!$C$20</f>
         <v/>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Ticket 500 a 1.500.</t>
         </is>
@@ -1262,11 +1285,11 @@
           <t>&gt;2,5</t>
         </is>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="28">
         <f>'Modelo'!$C$45</f>
         <v/>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Con cuotas. Sobre cobranza completa, sumá lo que falta cobrar.</t>
         </is>
@@ -1275,10 +1298,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -1291,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D43"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1300,44 +1323,51 @@
     <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Glosario</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Los términos que usa este modelo, en el orden del embudo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Término</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Qué es</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Dónde aparece</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Costo por mil impresiones: lo que cobra la plataforma de anuncios por mostrar el aviso mil veces.</t>
         </is>
@@ -1349,12 +1379,12 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>CTR</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de impresiones que terminan en clic al enlace.</t>
         </is>
@@ -1366,12 +1396,12 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Clic → visita</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de clics que llegan a cargar la página. Siempre menor a 100 % (cierran antes de que cargue).</t>
         </is>
@@ -1383,12 +1413,12 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Unidad de adquisición</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Lo que compra la publicidad en este embudo (visita, registro o entrada). Todo el modelo se mide por unidad.</t>
         </is>
@@ -1400,12 +1430,12 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Costo por unidad</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Inversión dividida por unidades compradas: costo por visita, CPL (costo por lead o registro) o costo por entrada.</t>
         </is>
@@ -1417,12 +1447,12 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Conversión</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Porcentaje que pasa de una etapa a la siguiente. Las conversiones se multiplican: 15 % × 14 % × 44 % = 0,9 %.</t>
         </is>
@@ -1434,12 +1464,12 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Show rate</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de registrados (o compradores) que asisten en vivo. El replay se cuenta aparte.</t>
         </is>
@@ -1451,12 +1481,12 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Oferta extra en el mismo checkout, con una casilla. Se mide como % de los compradores.</t>
         </is>
@@ -1468,12 +1498,12 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>OTO / upsell</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Oferta que aparece después de pagar (one-time offer). Downsell: la oferta más barata para quien rechaza la OTO.</t>
         </is>
@@ -1485,12 +1515,12 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Producto de mayor valor que se vende después del primero, por ascenso o por llamada.</t>
         </is>
@@ -1502,12 +1532,12 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Facturado promedio por comprador del producto principal, sumando toda la escalera.</t>
         </is>
@@ -1519,12 +1549,12 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>CPA / CAC</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Costo por comprador: inversión dividida por ventas del producto principal.</t>
         </is>
@@ -1536,12 +1566,12 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Facturado</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Lo vendido a precio de lista, aunque todavía no se haya cobrado (cuotas).</t>
         </is>
@@ -1553,12 +1583,12 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Cash cobrado</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Lo que efectivamente entró. Con cuotas, entra en varios meses según la curva de cobranza.</t>
         </is>
@@ -1570,12 +1600,12 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Cash neto</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Cash cobrado menos comisiones de pasarela, comisiones de ventas y reembolsos. Es la base de verdad del modelo.</t>
         </is>
@@ -1587,12 +1617,12 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Retorno sobre la inversión en publicidad. Sobre facturado, sobre cash o sobre cash neto: siempre decí cuál.</t>
         </is>
@@ -1604,12 +1634,12 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Valor neto por unidad (VPU)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Cash neto que deja cada unidad de adquisición, descontando los costos que crecen con el volumen. Es lo que vale un lead, una visita o una entrada.</t>
         </is>
@@ -1621,12 +1651,12 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Techo</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Costo por unidad al que no ganás ni perdés (break-even). Es igual al valor neto por unidad.</t>
         </is>
@@ -1638,12 +1668,12 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Techo dividido por (1 + margen de seguridad). Si pagás eso o menos, estás en verde.</t>
         </is>
@@ -1655,12 +1685,12 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Colchón entre el techo y el objetivo para absorber varianza, reembolsos y costos que no viste. 30 % es el estándar.</t>
         </is>
@@ -1672,12 +1702,12 @@
       </c>
     </row>
     <row r="26" ht="60" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Semáforo</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Rojo: el costo por unidad está por encima del techo (perdés con cada unidad). Verde: el costo está en el objetivo o por debajo y el ROAS sobre cash neto llega al objetivo. Amarillo: todo lo demás (el costo está entre objetivo y techo, o el ROAS no llega).</t>
         </is>
@@ -1689,12 +1719,12 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Techo móvil</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Mediana del valor neto por unidad de tus últimas 4 columnas de Seguimiento. Es el techo que se usa para decidir, porque refleja tu rendimiento reciente.</t>
         </is>
@@ -1706,12 +1736,12 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Conjunto de supuestos conservador, base u optimista. Se elige con una celda en Supuestos.</t>
         </is>
@@ -1723,12 +1753,12 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Sensibilidad</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Cuánto cambia la ganancia si mejorás una sola variable un 10 %. Dice qué palanca trabajar primero.</t>
         </is>
@@ -1740,12 +1770,12 @@
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Ganancia por visita / por lead / por cliente</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>La ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo por paso. La ganancia por visita es la métrica que más vale: resume todo lo que pasa después de la página.</t>
         </is>
@@ -1757,12 +1787,12 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Order value (AOV)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Facturado promedio por comprador del principal sumando toda la escalera. El AOV neto es lo mismo después de comisiones y reembolsos, y su par es el CPA.</t>
         </is>
@@ -1774,12 +1804,12 @@
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Caja necesaria</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>El peor momento de la ganancia acumulada en la proyección, en positivo. Es la plata que necesitás tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
         </is>
@@ -1791,12 +1821,12 @@
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Unit economics</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Los números por unidad: cuánto cuesta y cuánto deja cada visita, registro, entrada o comprador.</t>
         </is>
@@ -1808,12 +1838,12 @@
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Tráfico frío</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Gente que no te conoce y llega desde un anuncio. Convierte menos que tu audiencia propia.</t>
         </is>
@@ -1825,12 +1855,12 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Front / producto principal</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>El primer producto que se vende en el embudo. Todo lo demás (bumps, OTOs, programa) se mide como % de sus compradores.</t>
         </is>
@@ -1842,12 +1872,12 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Pitch</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>La parte del webinar o la llamada donde se presenta la oferta.</t>
         </is>
@@ -1859,12 +1889,12 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>VSL</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Video de ventas: la página de ventas es un video largo que vende el producto.</t>
         </is>
@@ -1876,12 +1906,12 @@
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Negocios que venden a empresas. Sus benchmarks de asistencia son más altos que los de tráfico frío a personas.</t>
         </is>
@@ -1893,12 +1923,12 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Self-serve</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Venta sin llamada: la persona compra sola desde una página de pago.</t>
         </is>
@@ -1910,12 +1940,12 @@
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Aplicación</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Formulario largo que el lead completa para pedir una llamada. Filtra y le da información al closer.</t>
         </is>
@@ -1927,12 +1957,12 @@
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Setter</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Persona que contacta a los que aplicaron, confirma y agenda. Cobra por contacto o por agenda.</t>
         </is>
@@ -1944,12 +1974,12 @@
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Closer</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Quien hace la llamada de venta. Cobra comisión sobre el cash cobrado.</t>
         </is>
@@ -1961,12 +1991,12 @@
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Show de la llamada</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de agendas que efectivamente ocurren.</t>
         </is>
@@ -1980,10 +2010,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -1996,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2005,32 +2035,39 @@
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Chequeos: el modelo se revisa solo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Si alguna fila dice REVISAR, hay un supuesto fuera de rango o un dato inconsistente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Chequeo</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Qué revisar</t>
         </is>
@@ -2042,11 +2079,11 @@
           <t>Ninguna celda con error en Modelo</t>
         </is>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="37">
         <f>IF(ISERROR(SUM('Modelo'!C5:C160)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2058,11 +2095,11 @@
           <t>Ninguna celda con error en Embudo</t>
         </is>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="37">
         <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2074,11 +2111,11 @@
           <t>Ninguna celda con error en Resumen</t>
         </is>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="37">
         <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2090,11 +2127,11 @@
           <t>Ninguna celda con error en Proyección 12 meses</t>
         </is>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="37">
         <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2106,11 +2143,11 @@
           <t>Ninguna celda con error en Escenarios</t>
         </is>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="37">
         <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2122,11 +2159,11 @@
           <t>Ninguna celda con error en Seguimiento</t>
         </is>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="37">
         <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2138,11 +2175,11 @@
           <t>Los supuestos de tráfico son mayores a cero</t>
         </is>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="37">
         <f>IF(AND('Supuestos'!$C$9&gt;0,'Supuestos'!$C$10&gt;0,'Supuestos'!$C$11&gt;0,'Supuestos'!$C$14&gt;0),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
         </is>
@@ -2154,11 +2191,11 @@
           <t>La curva de cobranza suma 100 %</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>IF(ABS('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42-1)&lt;0.001,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
         </is>
@@ -2170,11 +2207,11 @@
           <t>Comisiones + reembolsos menores al 60 %</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>IF(('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)&lt;0.6,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Si suman más, revisá los porcentajes.</t>
         </is>
@@ -2186,11 +2223,11 @@
           <t>El escenario en uso es 1, 2 o 3</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="37">
         <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Supuestos → celda 'Escenario en uso'.</t>
         </is>
@@ -2202,11 +2239,11 @@
           <t>La inversión es mayor a cero</t>
         </is>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -2214,11 +2251,11 @@
           <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
         </is>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="37">
         <f>IF('Modelo'!$C$25&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
         </is>
@@ -2230,11 +2267,11 @@
           <t>Las conversiones están entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="37">
         <f>IF(AND('Supuestos'!$C$10&gt;=0,'Supuestos'!$C$10&lt;=1,'Supuestos'!$C$11&gt;=0,'Supuestos'!$C$11&lt;=1,'Supuestos'!$C$14&gt;=0,'Supuestos'!$C$14&lt;=1,'Supuestos'!$C$18&gt;=0,'Supuestos'!$C$18&lt;=1,'Supuestos'!$C$21&gt;=0,'Supuestos'!$C$21&lt;=1,'Supuestos'!$C$22&gt;=0,'Supuestos'!$C$22&lt;=1,'Supuestos'!$C$23&gt;=0,'Supuestos'!$C$23&lt;=1,'Supuestos'!$C$24&gt;=0,'Supuestos'!$C$24&lt;=1,'Supuestos'!$C$25&gt;=0,'Supuestos'!$C$25&lt;=1,'Supuestos'!$C$30&gt;=0,'Supuestos'!$C$30&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
         </is>
@@ -2246,11 +2283,11 @@
           <t>El margen de seguridad está entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="37">
         <f>IF(AND('Supuestos'!$C$46&gt;=0,'Supuestos'!$C$46&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -2258,11 +2295,11 @@
           <t>El crecimiento mensual está entre −50 % y 100 %</t>
         </is>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="37">
         <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Más de 100 % por mes no es realista para una proyección.</t>
         </is>
@@ -2274,11 +2311,11 @@
           <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
         </is>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="37">
         <f>IF(AND('Modelo'!$C$15&lt;='Modelo'!$C$11,'Modelo'!$C$16&lt;='Modelo'!$C$15,'Modelo'!$C$17&lt;='Modelo'!$C$16,'Modelo'!$C$18&lt;='Modelo'!$C$17,'Modelo'!$C$23&lt;='Modelo'!$C$18),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Si falla, alguna conversión está por encima de 100 %.</t>
         </is>
@@ -2290,23 +2327,23 @@
           <t>El interruptor de evento previo es 0 o 1</t>
         </is>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="37">
         <f>IF(OR('Supuestos'!$C$17=0,'Supuestos'!$C$17=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Supuestos → evento previo.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Estado general del modelo</t>
         </is>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="38">
         <f>IF(COUNTIF(C6:C22,"REVISAR")=0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -2322,13 +2359,87 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Autoría y licencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Modelo financiero · Embudo de llamada (high ticket)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>v1.2 · octubre 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Licencia Creative Commons BY-NC-ND 4.0: podés usar este archivo con tus números y compartirlo tal cual, citando al autor. No podés venderlo, modificar su estructura para redistribuirlo ni quitar la línea de autoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Este archivo, sus fórmulas, sus umbrales y su método son obra de Jesús Tassarolo (TooAudience). Si lo compartís, compartilo entero y con esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Canal: youtube.com/@JesusTassaroloSinFiltro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2338,7 +2449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D41"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2347,45 +2458,52 @@
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Resumen: lo que hay que mirar</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Todo sale de Modelo con los supuestos del escenario en uso. Cambiá Supuestos y esto se actualiza.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Qué significa</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Resultado del mes</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2393,11 +2511,11 @@
           <t>Ganancia del período</t>
         </is>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <f>'Modelo'!$C$40</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Cash neto (cobranza completa) menos costos y menos inversión.</t>
         </is>
@@ -2409,11 +2527,11 @@
           <t>ROAS sobre cash neto</t>
         </is>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>'Modelo'!$C$42</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Sobre cash neto con la cobranza completa.</t>
         </is>
@@ -2425,11 +2543,11 @@
           <t>ROAS del cash del primer mes (sin cuotas futuras)</t>
         </is>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <f>'Modelo'!$C$45</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Solo con lo que entra el primer mes. Si es menor a 1, el mes se financia con caja.</t>
         </is>
@@ -2441,11 +2559,11 @@
           <t>Ventas del programa</t>
         </is>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Ventas del programa por mes.</t>
         </is>
@@ -2457,24 +2575,24 @@
           <t>Facturado total</t>
         </is>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="9">
         <f>'Modelo'!$C$29</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>A precio de lista, incluidas las cuotas por cobrar.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>La cadena</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -2482,11 +2600,11 @@
           <t>Leads</t>
         </is>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="12">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Leads que compra la pauta.</t>
         </is>
@@ -2498,11 +2616,11 @@
           <t>Agendas</t>
         </is>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="11">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Llamadas agendadas.</t>
         </is>
@@ -2514,11 +2632,11 @@
           <t>Llamadas realizadas</t>
         </is>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="11">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Llamadas que ocurren.</t>
         </is>
@@ -2530,11 +2648,11 @@
           <t>Costo por agenda</t>
         </is>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="13">
         <f>'Modelo'!$C$20</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Lo que te cuesta cada agenda.</t>
         </is>
@@ -2546,24 +2664,24 @@
           <t>Costo por venta del programa (CAC)</t>
         </is>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="13">
         <f>'Modelo'!$C$26</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Lo que te cuesta cada venta (CAC).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Las dos caras de cada número</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -2571,11 +2689,11 @@
           <t>Ganancia por visita</t>
         </is>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="13">
         <f>'Modelo'!$C$62</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada visita a la página. La métrica más valiosa del embudo.</t>
         </is>
@@ -2587,11 +2705,11 @@
           <t>Ganancia por clic</t>
         </is>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="13">
         <f>'Modelo'!$C$63</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada clic. Su par es el costo por clic (Embudo).</t>
         </is>
@@ -2603,11 +2721,11 @@
           <t>Ganancia por lead</t>
         </is>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="13">
         <f>'Modelo'!$C$64</f>
         <v/>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada lead. Su par es el CPL.</t>
         </is>
@@ -2619,11 +2737,11 @@
           <t>Ganancia por agenda</t>
         </is>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="13">
         <f>'Modelo'!$C$65</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada agenda. Su par es el costo por agenda.</t>
         </is>
@@ -2635,11 +2753,11 @@
           <t>Ganancia por cliente</t>
         </is>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="13">
         <f>'Modelo'!$C$67</f>
         <v/>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada cliente. Su par es el CAC.</t>
         </is>
@@ -2651,11 +2769,11 @@
           <t>Order value (AOV)</t>
         </is>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="13">
         <f>'Modelo'!$C$30</f>
         <v/>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Facturado por comprador del programa, con el downsell.</t>
         </is>
@@ -2667,24 +2785,24 @@
           <t>Order value neto (AOV neto)</t>
         </is>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="13">
         <f>'Modelo'!$C$61</f>
         <v/>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Lo mismo después de comisiones, reembolsos y costos por lead.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Hasta cuánto pagar</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -2692,11 +2810,11 @@
           <t>Techo de CPL (break-even)</t>
         </is>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="13">
         <f>'Modelo'!$C$48</f>
         <v/>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>CPL donde no ganás ni perdés.</t>
         </is>
@@ -2708,11 +2826,11 @@
           <t>Objetivo de CPL</t>
         </is>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="13">
         <f>'Modelo'!$C$49</f>
         <v/>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>A este CPL o menos estás en verde.</t>
         </is>
@@ -2724,11 +2842,11 @@
           <t>Techo de costo por agenda</t>
         </is>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="13">
         <f>'Modelo'!$C$51</f>
         <v/>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Costo máximo por agenda.</t>
         </is>
@@ -2740,11 +2858,11 @@
           <t>Techo de costo por venta (CAC máximo)</t>
         </is>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="13">
         <f>'Modelo'!$C$53</f>
         <v/>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>CAC máximo si lo demás se mantiene.</t>
         </is>
@@ -2756,24 +2874,24 @@
           <t>Semáforo del CPL actual</t>
         </is>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="14">
         <f>'Modelo'!$C$56</f>
         <v/>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Tu CPL actual contra techo y objetivo.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Cuánto invertir y cuánta caja</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -2781,11 +2899,11 @@
           <t>Inversión necesaria para la meta de ventas (al CPL actual)</t>
         </is>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="9">
         <f>'Modelo'!$C$57</f>
         <v/>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Para la meta de ventas de Supuestos, al CPL actual.</t>
         </is>
@@ -2797,11 +2915,11 @@
           <t>Llamadas que hay que atender por mes para esa meta</t>
         </is>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="11">
         <f>'Modelo'!$C$59</f>
         <v/>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Para dimensionar el equipo de closers.</t>
         </is>
@@ -2813,11 +2931,11 @@
           <t>Caja que hay que tener (peor momento de la proyección)</t>
         </is>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="9">
         <f>'Proyección 12 meses'!$C$18</f>
         <v/>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Si da 0, el embudo se autofinancia: cada mes cobra más de lo que invierte.</t>
         </is>
@@ -2829,11 +2947,11 @@
           <t>Saldo mínimo de caja con tu caja inicial</t>
         </is>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="9">
         <f>'Proyección 12 meses'!$C$19</f>
         <v/>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Si es negativo, la caja inicial no alcanza.</t>
         </is>
@@ -2845,30 +2963,30 @@
           <t>Ganancia acumulada en 12 meses</t>
         </is>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="9">
         <f>'Proyección 12 meses'!$C$20</f>
         <v/>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Con la inversión creciendo según el supuesto.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Recomendación según el semáforo</t>
         </is>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <f>IF('Modelo'!$C$56="VERDE","Sostener o subir un escalón (+25 %) y medir 7 días",IF('Modelo'!$C$56="AMARILLO","No subir. Si el costo está bien, el ROAS no llega al objetivo: mirá Sensibilidad. Si no, revisar en orden: CPM, creativo, página",IF('Modelo'!$C$56="ROJO","Bajar un escalón (−25 %) y arreglar antes de volver a subir","")))</f>
         <v/>
       </c>
-      <c r="D39" s="15" t="n"/>
+      <c r="D39" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · v1.2 · octubre 2026</t>
         </is>
@@ -2891,10 +3009,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -2907,7 +3025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2921,57 +3039,64 @@
     <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Embudo: todos los pasos, cuántos pasan y, por cada uno, qué pagás, qué te queda y hasta cuánto podrías pagar</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). Tres números por paso: lo que pagás hoy por cada uno (inversión ÷ cantidad), lo que te queda por cada uno (ganancia ÷ cantidad) y lo máximo que podrías pagar (el techo: lo que cada uno genera en cash neto). Techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>% que pasa</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>% acumulado</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Costo por paso (pagás hoy)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Ganancia por paso (te queda)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Techo por paso (máximo a pagar)</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Qué se paga acá / cómo se lee</t>
         </is>
@@ -2983,7 +3108,7 @@
           <t>Impresiones del anuncio (por mil)</t>
         </is>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
@@ -2997,19 +3122,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8*1000/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="13">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$40*1000/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="13">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1000/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Costo por mil impresiones (CPM) y CPM máximo.</t>
         </is>
@@ -3021,11 +3146,11 @@
           <t>Clics al enlace</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$8/'Modelo'!$C$7)</f>
         <v/>
       </c>
@@ -3034,19 +3159,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>IF('Modelo'!$C$8=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$40*1/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Costo por clic (CTR).</t>
         </is>
@@ -3058,11 +3183,11 @@
           <t>Visitas a la página</t>
         </is>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="17">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3071,55 +3196,55 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$40*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Costo por visita.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Leads</t>
         </is>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="17">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$11/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <f>IF('Modelo'!$C$11=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$40*1/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="13">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>CPL real.</t>
         </is>
@@ -3131,31 +3256,31 @@
           <t>Asisten al evento previo (si hay)</t>
         </is>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="17">
         <f>'Modelo'!$C$13</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$13/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$13/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>IF('Modelo'!$C$13=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$13)</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>IF('Modelo'!$C$13=0,0,'Modelo'!$C$40*1/'Modelo'!$C$13)</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <f>IF('Modelo'!$C$13=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$13)</f>
         <v/>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Solo cuenta con el interruptor de evento en 1; si no, queda en 0.</t>
         </is>
@@ -3167,31 +3292,31 @@
           <t>Completan la aplicación</t>
         </is>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="17">
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$15/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$15/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>IF('Modelo'!$C$15=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$40*1/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Costo por aplicación. Sobre leads (sobre asistentes si hay evento).</t>
         </is>
@@ -3203,67 +3328,67 @@
           <t>Califican</t>
         </is>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="17">
         <f>'Modelo'!$C$16</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$16/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$16/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>IF('Modelo'!$C$16=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$40*1/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Sobre aplicaciones. Palanca: las preguntas del formulario.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Agendan la llamada</t>
         </is>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="18">
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$17/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$17/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>IF('Modelo'!$C$17=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$40*1/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Costo por agenda. Sobre calificados. Palancas: setter, confirmación por WhatsApp.</t>
         </is>
@@ -3275,67 +3400,67 @@
           <t>Aparecen en la llamada (show)</t>
         </is>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="17">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="18">
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$18/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$18/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$40*1/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Costo por llamada realizada. Sobre agendas. Palancas: recordatorio, video de bienvenida.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Compran el programa</t>
         </is>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="17">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="18">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$23/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>IF('Modelo'!$C$23=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$40*1/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$47*'Modelo'!$C$11*1/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>CAC. Sobre llamadas (cierre). Juzgar con 3 a 4 eventos, nunca con uno.</t>
         </is>
@@ -3347,15 +3472,15 @@
           <t>Toman el downsell</t>
         </is>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="17">
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="18">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$24/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$24/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -3374,80 +3499,80 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Sobre llamadas que no compraron. Se pagó con el CAC; suma al facturado.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Comprobalo con la fila de la unidad: costo + ganancia + fijos repartidos = techo</t>
         </is>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <f>F9</f>
         <v/>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>G9</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <f>F9+G9+'Supuestos'!$C$37/'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Techo = costo + ganancia + fijos ÷ unidades. Lo que falta entre (costo + ganancia) y el techo son los costos fijos repartidos entre las unidades.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Cómo se lee</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Cantidad: cuántas acciones o personas hubo en ese paso con los supuestos del escenario en uso.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Costo por paso: inversión ÷ cantidad. Es lo que te está costando hoy cada persona que llega a ese paso.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Ganancia por paso: ganancia del período ÷ cantidad. Lo que te queda por cada persona de ese paso después de pagar la pauta, las comisiones, los reembolsos y los fijos. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Techo por paso: lo que cada persona de ese paso genera en cash neto (cash neto menos costos por unidad, dividido por la cantidad). Es lo máximo que podrías pagar por ese paso antes de que la ganancia llegue a cero, si lo demás se mantiene. Por eso siempre es mayor que la ganancia: techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Los bumps, las OTOs y la ascensión no tienen costo propio: se pagan con el CPA del comprador principal y se miden por lo que suman al AOV.</t>
         </is>
@@ -3464,10 +3589,10 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -3480,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3493,64 +3618,71 @@
     <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Supuestos</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Celdas amarillas = las editás vos. Celdas azules = se calculan solas. Cada fila dice en qué unidad va y de dónde sale el valor del ejemplo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Supuesto</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor en uso</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Nota / fuente del ejemplo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Escenario en uso (1 = conservador · 2 = base · 3 = optimista)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="21" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -3558,24 +3690,24 @@
           <t>1 / 2 / 3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Cambia todas las filas que tienen tres valores. Si una fila no tiene tres valores, se usa el de 'Valor en uso'.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>1. Inversión y tráfico</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -3583,7 +3715,7 @@
           <t>Inversión en publicidad por mes</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="22" t="n">
         <v>4500</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -3591,7 +3723,7 @@
           <t>USD / mes</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>150 USD por día en el ejemplo.</t>
         </is>
@@ -3603,17 +3735,17 @@
           <t>CPM (costo por mil impresiones)</t>
         </is>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <f>IF('Supuestos'!$C$6=1,D9,IF('Supuestos'!$C$6=2,E9,F9))</f>
         <v/>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="23" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -3621,7 +3753,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Públicos de ticket alto suelen ser más caros: 7 a 15.</t>
         </is>
@@ -3633,17 +3765,17 @@
           <t>CTR al enlace</t>
         </is>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <f>IF('Supuestos'!$C$6=1,D10,IF('Supuestos'!$C$6=2,E10,F10))</f>
         <v/>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="24" t="n">
         <v>0.012</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="24" t="n">
         <v>0.015</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="24" t="n">
         <v>0.02</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -3651,7 +3783,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -3659,7 +3791,7 @@
           <t>% de clics que cargan la página</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="24" t="n">
         <v>0.85</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -3667,20 +3799,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>2. Página de captación</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -3688,17 +3820,17 @@
           <t>% de visitas que dejan sus datos (lead)</t>
         </is>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="18">
         <f>IF('Supuestos'!$C$6=1,D14,IF('Supuestos'!$C$6=2,E14,F14))</f>
         <v/>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="24" t="n">
         <v>0.28</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="24" t="n">
         <v>0.35</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -3706,24 +3838,24 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Registro al webinar o inicio de la aplicación.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>3. Evento previo (opcional)</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -3731,7 +3863,7 @@
           <t>¿Hay webinar o evento antes de la aplicación? (1 = sí, 0 = no)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="21" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -3739,7 +3871,7 @@
           <t>1 / 0</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Con 1, la aplicación se mide sobre los asistentes; con 0, sobre todos los leads.</t>
         </is>
@@ -3751,17 +3883,17 @@
           <t>% de leads que asisten al evento</t>
         </is>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="18">
         <f>IF('Supuestos'!$C$6=1,D18,IF('Supuestos'!$C$6=2,E18,F18))</f>
         <v/>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="24" t="n">
         <v>0.14</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="24" t="n">
         <v>0.2</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -3769,24 +3901,24 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Solo cuenta si el interruptor está en 1.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>4. Aplicación, agenda y llamada</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -3794,17 +3926,17 @@
           <t>% que completa la aplicación (de leads, o de asistentes si hay evento)</t>
         </is>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="18">
         <f>IF('Supuestos'!$C$6=1,D21,IF('Supuestos'!$C$6=2,E21,F21))</f>
         <v/>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="24" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F21" s="24" t="n">
         <v>0.15</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -3812,7 +3944,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Formulario largo con preguntas que califican.</t>
         </is>
@@ -3824,17 +3956,17 @@
           <t>% de aplicaciones que califican</t>
         </is>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="18">
         <f>IF('Supuestos'!$C$6=1,D22,IF('Supuestos'!$C$6=2,E22,F22))</f>
         <v/>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="F22" s="23" t="n">
+      <c r="F22" s="24" t="n">
         <v>0.7</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -3842,7 +3974,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Pasan el filtro de capacidad de inversión y perfil.</t>
         </is>
@@ -3854,17 +3986,17 @@
           <t>% de calificados que agendan</t>
         </is>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="18">
         <f>IF('Supuestos'!$C$6=1,D23,IF('Supuestos'!$C$6=2,E23,F23))</f>
         <v/>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="24" t="n">
         <v>0.45</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F23" s="24" t="n">
         <v>0.75</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -3872,7 +4004,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Mercado: 30 a 60 % de las aplicaciones terminan en agenda.</t>
         </is>
@@ -3884,17 +4016,17 @@
           <t>% de agendas que aparecen en la llamada</t>
         </is>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="18">
         <f>IF('Supuestos'!$C$6=1,D24,IF('Supuestos'!$C$6=2,E24,F24))</f>
         <v/>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="24" t="n">
         <v>0.7</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F24" s="24" t="n">
         <v>0.8</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -3902,7 +4034,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Mercado: 65 a 75 %. Confirmación por WhatsApp y video de bienvenida lo suben.</t>
         </is>
@@ -3914,17 +4046,17 @@
           <t>% de llamadas que compran</t>
         </is>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="18">
         <f>IF('Supuestos'!$C$6=1,D25,IF('Supuestos'!$C$6=2,E25,F25))</f>
         <v/>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="24" t="n">
         <v>0.18</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="F25" s="23" t="n">
+      <c r="F25" s="24" t="n">
         <v>0.35</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -3932,24 +4064,24 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Lead tibio y calificado: 20 a 40 %. Frío sin filtro: menos de 5 %.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>5. Oferta</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -3957,7 +4089,7 @@
           <t>Programa: precio</t>
         </is>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="23" t="n">
         <v>1500</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -3965,7 +4097,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Debajo de 1.500 un closer 1 a 1 rara vez se paga; el modelo te lo muestra en la ganancia.</t>
         </is>
@@ -3977,7 +4109,7 @@
           <t>Downsell para quien no compra en la llamada: precio</t>
         </is>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="23" t="n">
         <v>497</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -3985,7 +4117,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Versión reducida o self-serve.</t>
         </is>
@@ -3997,17 +4129,17 @@
           <t>Downsell: % de los que no compraron que lo toman</t>
         </is>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="18">
         <f>IF('Supuestos'!$C$6=1,D30,IF('Supuestos'!$C$6=2,E30,F30))</f>
         <v/>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="24" t="n">
         <v>0.05</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F30" s="24" t="n">
         <v>0.15</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -4015,20 +4147,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>6. Costos</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -4036,7 +4168,7 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="24" t="n">
         <v>0.05</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -4044,7 +4176,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Hotmart, Stripe, Mercado Pago: lo que se queda la plataforma.</t>
         </is>
@@ -4056,7 +4188,7 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="24" t="n">
         <v>0.1</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -4064,7 +4196,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Comisión de closers y setters sobre el cash cobrado. 10 a 15 % es lo común.</t>
         </is>
@@ -4076,7 +4208,7 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="24" t="n">
         <v>0.05</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -4084,7 +4216,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>5 % es normal en productos digitales. Más de 10 % es un problema de oferta o de expectativa.</t>
         </is>
@@ -4096,7 +4228,7 @@
           <t>Costos por lead (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="n">
+      <c r="C36" s="23" t="n">
         <v>0.2</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -4104,7 +4236,7 @@
           <t>USD / lead</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>WhatsApp, herramientas de agenda, setter por contacto.</t>
         </is>
@@ -4116,7 +4248,7 @@
           <t>Costos fijos por mes</t>
         </is>
       </c>
-      <c r="C37" s="21" t="n">
+      <c r="C37" s="22" t="n">
         <v>2500</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -4124,24 +4256,24 @@
           <t>USD / mes</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Equipo, herramientas, edición: lo que pagás aunque no vendas.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>7. Cobranza</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -4149,7 +4281,7 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C40" s="23" t="n">
+      <c r="C40" s="24" t="n">
         <v>0.6</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -4157,7 +4289,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Ticket alto con cuotas: 60 % al contado o primera cuota, el resto en dos meses.</t>
         </is>
@@ -4169,7 +4301,7 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C41" s="23" t="n">
+      <c r="C41" s="24" t="n">
         <v>0.2</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -4177,7 +4309,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Cuotas o pagos diferidos.</t>
         </is>
@@ -4189,7 +4321,7 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C42" s="23" t="n">
+      <c r="C42" s="24" t="n">
         <v>0.2</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -4197,24 +4329,24 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Los tres deben sumar 100 %.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>8. Objetivos y proyección</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -4222,7 +4354,7 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C45" s="24" t="n">
+      <c r="C45" s="25" t="n">
         <v>2.5</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -4230,7 +4362,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>El retorno mínimo que querés por cada dólar invertido, después de comisiones y reembolsos. Entra en el semáforo: sin llegar a este ROAS no hay verde.</t>
         </is>
@@ -4242,7 +4374,7 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C46" s="23" t="n">
+      <c r="C46" s="24" t="n">
         <v>0.3</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -4250,7 +4382,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Colchón entre el techo (donde no ganás ni perdés) y el objetivo. 30 % es el estándar que usamos.</t>
         </is>
@@ -4262,7 +4394,7 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n">
+      <c r="C47" s="21" t="n">
         <v>15</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -4270,7 +4402,7 @@
           <t>ventas / mes</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Para calcular cuánto invertir.</t>
         </is>
@@ -4282,7 +4414,7 @@
           <t>Crecimiento de la inversión por mes (proyección)</t>
         </is>
       </c>
-      <c r="C48" s="23" t="n">
+      <c r="C48" s="24" t="n">
         <v>0.1</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -4290,7 +4422,7 @@
           <t>% / mes</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Cuánto sube la inversión cada mes en la proyección. 10 % por mes es un ritmo prudente; más de 25 % suele encarecer el CPM.</t>
         </is>
@@ -4302,7 +4434,7 @@
           <t>Caja inicial</t>
         </is>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C49" s="22" t="n">
         <v>8000</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -4310,7 +4442,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Con cuánta plata arrancás. La proyección te dice si alcanza.</t>
         </is>
@@ -4319,10 +4451,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -4335,7 +4467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D67"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4344,45 +4476,52 @@
     <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Modelo: la cadena completa del embudo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila es una etapa o un resultado. No se edita: todo sale de Supuestos. La columna de la derecha dice cómo se calcula.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Etapa / resultado</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Cómo se calcula</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Tráfico y leads</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -4390,11 +4529,11 @@
           <t>Impresiones</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>IF('Supuestos'!$C$9=0,0,'Supuestos'!$C$8/'Supuestos'!$C$9*1000)</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ CPM × 1.000.</t>
         </is>
@@ -4406,11 +4545,11 @@
           <t>Clics al enlace</t>
         </is>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="17">
         <f>'Modelo'!$C$7*'Supuestos'!$C$10</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Impresiones × CTR.</t>
         </is>
@@ -4422,56 +4561,56 @@
           <t>Visitas a la página</t>
         </is>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="17">
         <f>'Modelo'!$C$8*'Supuestos'!$C$11</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Clics × % que carga.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Costo por lead (CPL)</t>
         </is>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="13">
         <f>IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14))</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>CPM ÷ 1.000 ÷ (CTR × clic→visita × conversión de la página).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Leads</t>
         </is>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="12">
         <f>IF('Modelo'!$C$10=0,0,'Supuestos'!$C$8/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ CPL.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Evento, aplicación y agenda</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -4479,11 +4618,11 @@
           <t>Asistentes al evento (si hay)</t>
         </is>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f>IF('Supuestos'!$C$17=1,'Modelo'!$C$11*'Supuestos'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Leads × asistencia, solo con el interruptor en 1.</t>
         </is>
@@ -4495,11 +4634,11 @@
           <t>Base de la aplicación (asistentes o leads)</t>
         </is>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="17">
         <f>IF('Supuestos'!$C$17=1,'Modelo'!$C$13,'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Sobre quién se mide la aplicación.</t>
         </is>
@@ -4511,11 +4650,11 @@
           <t>Aplicaciones completas</t>
         </is>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="17">
         <f>'Modelo'!$C$14*'Supuestos'!$C$21</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Base × % que aplica.</t>
         </is>
@@ -4527,27 +4666,27 @@
           <t>Calificados</t>
         </is>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="17">
         <f>'Modelo'!$C$15*'Supuestos'!$C$22</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Aplicaciones × % que califica.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Agendas</t>
         </is>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="11">
         <f>'Modelo'!$C$16*'Supuestos'!$C$23</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Calificados × % que agenda.</t>
         </is>
@@ -4559,11 +4698,11 @@
           <t>Llamadas realizadas</t>
         </is>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <f>'Modelo'!$C$17*'Supuestos'!$C$24</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Agendas × show de la llamada.</t>
         </is>
@@ -4575,27 +4714,27 @@
           <t>Costo por aplicación</t>
         </is>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <f>IF('Modelo'!$C$15=0,0,'Supuestos'!$C$8/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ aplicaciones.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Costo por agenda</t>
         </is>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="13">
         <f>IF('Modelo'!$C$17=0,0,'Supuestos'!$C$8/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ agendas.</t>
         </is>
@@ -4607,36 +4746,36 @@
           <t>Costo por llamada realizada</t>
         </is>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ llamadas.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Ventas y facturación</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Ventas del programa</t>
         </is>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="11">
         <f>'Modelo'!$C$18*'Supuestos'!$C$25</f>
         <v/>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Llamadas × cierre.</t>
         </is>
@@ -4648,11 +4787,11 @@
           <t>Ventas del downsell</t>
         </is>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>('Modelo'!$C$18-'Modelo'!$C$23)*'Supuestos'!$C$30</f>
         <v/>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>(Llamadas − ventas) × % que toma el downsell.</t>
         </is>
@@ -4664,27 +4803,27 @@
           <t>% de leads que compran el programa</t>
         </is>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Ventas ÷ leads.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Costo por venta del programa (CAC)</t>
         </is>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="13">
         <f>IF('Modelo'!$C$23=0,0,'Supuestos'!$C$8/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ ventas.</t>
         </is>
@@ -4696,11 +4835,11 @@
           <t>Facturado: programa</t>
         </is>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="27">
         <f>'Modelo'!$C$23*'Supuestos'!$C$28</f>
         <v/>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4712,27 +4851,27 @@
           <t>Facturado: downsell</t>
         </is>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <f>'Modelo'!$C$24*'Supuestos'!$C$29</f>
         <v/>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Facturado total</t>
         </is>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="9">
         <f>'Modelo'!$C$27+'Modelo'!$C$28</f>
         <v/>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Programa + downsell.</t>
         </is>
@@ -4744,11 +4883,11 @@
           <t>Facturado por comprador del programa</t>
         </is>
       </c>
-      <c r="C30" s="19">
+      <c r="C30" s="20">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$29/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Facturado ÷ ventas del programa.</t>
         </is>
@@ -4760,11 +4899,11 @@
           <t>Ventas del programa por lead (para la proyección)</t>
         </is>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="19">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Igual a '% de leads que compran'.</t>
         </is>
@@ -4776,24 +4915,24 @@
           <t>Facturado por lead</t>
         </is>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$29/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Facturado ÷ leads.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Cash, costos y ganancia del período</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
@@ -4801,11 +4940,11 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <f>'Modelo'!$C$29*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42)</f>
         <v/>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Facturado × (mes 1 + mes 2 + mes 3). Si la cobranza suma 100 %, es igual al facturado.</t>
         </is>
@@ -4817,11 +4956,11 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="27">
         <f>'Modelo'!$C$29*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Facturado × % del mes 1.</t>
         </is>
@@ -4833,11 +4972,11 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="27">
         <f>'Modelo'!$C$34*('Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Cash × (pasarela + equipo de ventas).</t>
         </is>
@@ -4849,27 +4988,27 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="27">
         <f>'Modelo'!$C$34*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Cash × % de reembolsos.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Cash neto</t>
         </is>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="9">
         <f>'Modelo'!$C$34*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Cash − comisiones − reembolsos. La base de verdad.</t>
         </is>
@@ -4881,27 +5020,27 @@
           <t>Costos por lead (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="27">
         <f>'Modelo'!$C$11*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Leads × costo por lead.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período</t>
         </is>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="9">
         <f>'Modelo'!$C$38-'Modelo'!$C$39-'Supuestos'!$C$37-'Supuestos'!$C$8</f>
         <v/>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Cash neto − costos por unidad − fijos − inversión.</t>
         </is>
@@ -4913,27 +5052,27 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="28">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$29/'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Facturado ÷ inversión. El número que más se infla: no decidas con este.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto</t>
         </is>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="10">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$38/'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Cash neto ÷ inversión. Con este se decide.</t>
         </is>
@@ -4945,11 +5084,11 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="18">
         <f>IF('Modelo'!$C$34=0,0,'Modelo'!$C$40/'Modelo'!$C$34)</f>
         <v/>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Ganancia ÷ cash.</t>
         </is>
@@ -4961,84 +5100,84 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>IF('Modelo'!$C$42&gt;='Supuestos'!$C$45,"SÍ","NO")</f>
         <v/>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto contra el objetivo de Supuestos.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>ROAS del cash del primer mes (sin cuotas futuras)</t>
         </is>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="10">
         <f>'Modelo'!$C$35*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/'Supuestos'!$C$8</f>
         <v/>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Lo que vuelve el mismo mes. Si es menor a 1, el mes se financia con caja.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Cuánto vale cada lead y hasta cuánto pagar</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Valor neto por lead</t>
         </is>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="13">
         <f>IF('Modelo'!$C$11=0,0,('Modelo'!$C$38-'Modelo'!$C$39)/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>(Cash neto − costos por lead) ÷ leads.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Techo de CPL (break-even)</t>
         </is>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="13">
         <f>'Modelo'!$C$47</f>
         <v/>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Igual al valor neto por lead.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Objetivo de CPL</t>
         </is>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="13">
         <f>'Modelo'!$C$48/(1+'Supuestos'!$C$46)</f>
         <v/>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Techo ÷ (1 + margen de seguridad).</t>
         </is>
@@ -5050,27 +5189,27 @@
           <t>Techo de costo por aplicación</t>
         </is>
       </c>
-      <c r="C50" s="19">
+      <c r="C50" s="20">
         <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$47*'Modelo'!$C$11/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Valor total ÷ aplicaciones.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Techo de costo por agenda</t>
         </is>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="13">
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$47*'Modelo'!$C$11/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Valor total ÷ agendas.</t>
         </is>
@@ -5082,11 +5221,11 @@
           <t>Techo de costo por llamada realizada</t>
         </is>
       </c>
-      <c r="C52" s="19">
+      <c r="C52" s="20">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$47*'Modelo'!$C$11/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Valor total ÷ llamadas.</t>
         </is>
@@ -5098,11 +5237,11 @@
           <t>Techo de costo por venta (CAC máximo)</t>
         </is>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="20">
         <f>IF('Modelo'!$C$25=0,0,'Modelo'!$C$47/'Modelo'!$C$25)</f>
         <v/>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Valor por lead ÷ % de leads que compran.</t>
         </is>
@@ -5114,52 +5253,52 @@
           <t>Objetivo de CAC</t>
         </is>
       </c>
-      <c r="C54" s="19">
+      <c r="C54" s="20">
         <f>'Modelo'!$C$53/(1+'Supuestos'!$C$46)</f>
         <v/>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>CAC máximo ÷ (1 + margen de seguridad).</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Semáforo y cuánto invertir</t>
         </is>
       </c>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Semáforo del CPL actual</t>
         </is>
       </c>
-      <c r="C56" s="13">
+      <c r="C56" s="14">
         <f>IF('Modelo'!$C$10&gt;'Modelo'!$C$48,"ROJO",IF(AND('Modelo'!$C$10&lt;='Modelo'!$C$49,'Modelo'!$C$42&gt;='Supuestos'!$C$45),"VERDE","AMARILLO"))</f>
         <v/>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Rojo: costo &gt; techo. Verde: costo ≤ objetivo y ROAS sobre cash neto ≥ objetivo. Amarillo: el resto.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Inversión necesaria para la meta de ventas (al CPL actual)</t>
         </is>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="9">
         <f>IF('Modelo'!$C$25=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Modelo'!$C$25*'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Meta ÷ % de leads que compran × CPL.</t>
         </is>
@@ -5171,11 +5310,11 @@
           <t>Inversión para la meta al CPL objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="C58" s="26">
+      <c r="C58" s="27">
         <f>IF('Modelo'!$C$25=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Modelo'!$C$25*'Modelo'!$C$49)</f>
         <v/>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Lo mismo, al CPL objetivo.</t>
         </is>
@@ -5187,52 +5326,52 @@
           <t>Llamadas que hay que atender por mes para esa meta</t>
         </is>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="26">
         <f>IF('Supuestos'!$C$25=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Supuestos'!$C$25)</f>
         <v/>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Meta ÷ cierre. Sirve para dimensionar closers.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Ganancia por paso (las dos caras de cada número: costo por X y ganancia por X)</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Cash neto por comprador (AOV neto)</t>
         </is>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="13">
         <f>IF('Modelo'!$C$23=0,0,('Modelo'!$C$38-'Modelo'!$C$39)/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Lo que deja cada comprador del principal después de comisiones, reembolsos y costos por unidad. Su par es el CPA.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Ganancia por visita</t>
         </is>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="13">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$40/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ visitas a la página. La métrica más valiosa: resume todo lo que pasa después. Su par es el costo por visita.</t>
         </is>
@@ -5244,27 +5383,27 @@
           <t>Ganancia por clic</t>
         </is>
       </c>
-      <c r="C63" s="19">
+      <c r="C63" s="20">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$40/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ clics. Su par es el costo por clic.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Ganancia por lead</t>
         </is>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="13">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$40/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ leads. Su par es el CPL.</t>
         </is>
@@ -5276,11 +5415,11 @@
           <t>Ganancia por agenda</t>
         </is>
       </c>
-      <c r="C65" s="19">
+      <c r="C65" s="20">
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$40/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ agendas. Su par es el costo por agenda.</t>
         </is>
@@ -5292,27 +5431,27 @@
           <t>Ganancia por llamada</t>
         </is>
       </c>
-      <c r="C66" s="19">
+      <c r="C66" s="20">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$40/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ llamadas. Su par es el costo por llamada.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Ganancia por cliente</t>
         </is>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="13">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$40/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ compradores. Su par es el CAC.</t>
         </is>
@@ -5332,10 +5471,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -5348,7 +5487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5364,15 +5503,22 @@
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Escenarios: qué pasa si cambian el precio, la conversión o el costo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Las celdas amarillas de cada tabla (fila y columna) se pueden cambiar. Verde = ganancia, amarillo = cerca del cero, rojo = pérdida. Todo lo demás queda como en Supuestos.</t>
         </is>
@@ -5384,705 +5530,705 @@
           <t>Umbral de 'cerca del cero' (inversión × margen de seguridad)</t>
         </is>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$46</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Precio del programa × % de llamadas que compran → ganancia del mes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>A más precio, menos cierre: la tabla muestra desde qué ticket el closer se paga.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Precio ↓  /  % cierre →</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.15</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="30" t="n">
         <v>0.35</v>
       </c>
-      <c r="H9" s="29" t="n">
+      <c r="H9" s="30" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="31" t="n">
         <v>497</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="31" t="n">
         <v>997</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="31" t="n">
         <v>1500</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="31" t="n">
         <v>2500</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="n">
+      <c r="B14" s="31" t="n">
         <v>3500</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>CPL × % de llamadas que compran → ganancia del mes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Hasta qué CPL seguís ganando según el cierre.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>CPL ↓  /  % cierre →</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.15</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="30" t="n">
         <v>0.35</v>
       </c>
-      <c r="H20" s="29" t="n">
+      <c r="H20" s="30" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G26" s="26">
+      <c r="G26" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Cuánto invertir para una facturación objetivo por mes, según el ROAS que querés</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Inversión = facturación ÷ ROAS. Debajo: cuántos leads hacen falta y cuánto podés pagar por cada uno.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Facturación objetivo ↓ / ROAS objetivo →</t>
         </is>
       </c>
-      <c r="C32" s="32" t="n">
+      <c r="C32" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="32" t="n">
+      <c r="D32" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="32" t="n">
+      <c r="E32" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="32" t="n">
+      <c r="F32" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G32" s="32" t="n">
+      <c r="G32" s="33" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="31" t="n">
         <v>20000</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="27">
         <f>$B33/C$32</f>
         <v/>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="27">
         <f>$B33/D$32</f>
         <v/>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="27">
         <f>$B33/E$32</f>
         <v/>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="27">
         <f>$B33/F$32</f>
         <v/>
       </c>
-      <c r="G33" s="26">
+      <c r="G33" s="27">
         <f>$B33/G$32</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="31" t="n">
         <v>50000</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <f>$B34/C$32</f>
         <v/>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="27">
         <f>$B34/D$32</f>
         <v/>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="27">
         <f>$B34/E$32</f>
         <v/>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="27">
         <f>$B34/F$32</f>
         <v/>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="27">
         <f>$B34/G$32</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="31" t="n">
         <v>100000</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="27">
         <f>$B35/C$32</f>
         <v/>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="27">
         <f>$B35/D$32</f>
         <v/>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="27">
         <f>$B35/E$32</f>
         <v/>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="27">
         <f>$B35/F$32</f>
         <v/>
       </c>
-      <c r="G35" s="26">
+      <c r="G35" s="27">
         <f>$B35/G$32</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="31" t="n">
         <v>200000</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="27">
         <f>$B36/C$32</f>
         <v/>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="27">
         <f>$B36/D$32</f>
         <v/>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="27">
         <f>$B36/E$32</f>
         <v/>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="27">
         <f>$B36/F$32</f>
         <v/>
       </c>
-      <c r="G36" s="26">
+      <c r="G36" s="27">
         <f>$B36/G$32</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="31" t="n">
         <v>500000</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="27">
         <f>$B37/C$32</f>
         <v/>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="27">
         <f>$B37/D$32</f>
         <v/>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="27">
         <f>$B37/E$32</f>
         <v/>
       </c>
-      <c r="F37" s="26">
+      <c r="F37" s="27">
         <f>$B37/F$32</f>
         <v/>
       </c>
-      <c r="G37" s="26">
+      <c r="G37" s="27">
         <f>$B37/G$32</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Cantidad de leads necesaria para esa facturación</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="33">
+      <c r="B39" s="34">
         <f>$B33</f>
         <v/>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="17">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B33/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="33">
+      <c r="B40" s="34">
         <f>$B34</f>
         <v/>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="17">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B34/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="33">
+      <c r="B41" s="34">
         <f>$B35</f>
         <v/>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="17">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B35/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="33">
+      <c r="B42" s="34">
         <f>$B36</f>
         <v/>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="17">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B36/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="33">
+      <c r="B43" s="34">
         <f>$B37</f>
         <v/>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="17">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B37/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Costo máximo por lead para cumplir cada ROAS (sobre facturado)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="34" t="n">
+      <c r="C46" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="34" t="n">
+      <c r="D46" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E46" s="34" t="n">
+      <c r="E46" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="34" t="n">
+      <c r="F46" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="34" t="n">
+      <c r="G46" s="35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6092,65 +6238,65 @@
           <t>Costo máximo (facturado por unidad ÷ ROAS)</t>
         </is>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="20">
         <f>IF(C46=0,0,'Modelo'!$C$32/C46)</f>
         <v/>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="20">
         <f>IF(D46=0,0,'Modelo'!$C$32/D46)</f>
         <v/>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="20">
         <f>IF(E46=0,0,'Modelo'!$C$32/E46)</f>
         <v/>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="20">
         <f>IF(F46=0,0,'Modelo'!$C$32/F46)</f>
         <v/>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="20">
         <f>IF(G46=0,0,'Modelo'!$C$32/G46)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Sobre cash neto, el techo real está en Modelo (ya descuenta comisiones y reembolsos).</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Guardarraíl: el ROAS mínimo que tiene que dar cada nivel de inversión para que subir valga la pena</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Parte de tu inversión y tu ROAS actuales. Cada dólar extra tiene que devolver al menos 1,3 neto. Si al subir un escalón el ROAS real queda por debajo del mínimo de esa fila, volvé al escalón anterior.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Nivel de inversión</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Inversión del período</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>ROAS mínimo (cash neto)</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>Ganancia mínima</t>
         </is>
@@ -6162,15 +6308,15 @@
           <t>actual</t>
         </is>
       </c>
-      <c r="C54" s="26">
+      <c r="C54" s="27">
         <f>'Supuestos'!$C$8*1.0</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="28">
         <f>IF(C54=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C54-'Supuestos'!$C$8))/C54)</f>
         <v/>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="27">
         <f>C54*(D54-1)</f>
         <v/>
       </c>
@@ -6181,15 +6327,15 @@
           <t>× 1.25</t>
         </is>
       </c>
-      <c r="C55" s="26">
+      <c r="C55" s="27">
         <f>'Supuestos'!$C$8*1.25</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="28">
         <f>IF(C55=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C55-'Supuestos'!$C$8))/C55)</f>
         <v/>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="27">
         <f>C55*(D55-1)</f>
         <v/>
       </c>
@@ -6200,15 +6346,15 @@
           <t>× 1.5</t>
         </is>
       </c>
-      <c r="C56" s="26">
+      <c r="C56" s="27">
         <f>'Supuestos'!$C$8*1.5</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="28">
         <f>IF(C56=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C56-'Supuestos'!$C$8))/C56)</f>
         <v/>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="27">
         <f>C56*(D56-1)</f>
         <v/>
       </c>
@@ -6219,15 +6365,15 @@
           <t>× 2</t>
         </is>
       </c>
-      <c r="C57" s="26">
+      <c r="C57" s="27">
         <f>'Supuestos'!$C$8*2.0</f>
         <v/>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="28">
         <f>IF(C57=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C57-'Supuestos'!$C$8))/C57)</f>
         <v/>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="27">
         <f>C57*(D57-1)</f>
         <v/>
       </c>
@@ -6238,15 +6384,15 @@
           <t>× 3</t>
         </is>
       </c>
-      <c r="C58" s="26">
+      <c r="C58" s="27">
         <f>'Supuestos'!$C$8*3.0</f>
         <v/>
       </c>
-      <c r="D58" s="27">
+      <c r="D58" s="28">
         <f>IF(C58=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C58-'Supuestos'!$C$8))/C58)</f>
         <v/>
       </c>
-      <c r="E58" s="26">
+      <c r="E58" s="27">
         <f>C58*(D58-1)</f>
         <v/>
       </c>
@@ -6278,10 +6424,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -6294,7 +6440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6306,59 +6452,66 @@
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Sensibilidad: qué palanca mueve más la ganancia</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila mejora una sola variable un 10 % (o baja un costo un 10 %) y recalcula la ganancia del período. El ranking dice qué conviene trabajar primero.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Palanca</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Ganancia nueva</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Dif. %</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período con los supuestos actuales</t>
         </is>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>'Modelo'!$C$40</f>
         <v/>
       </c>
@@ -6374,19 +6527,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="18">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="17">
         <f>RANK(E7,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6402,19 +6555,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="17">
         <f>RANK(E8,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6430,19 +6583,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*('Supuestos'!$C$21*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*('Supuestos'!$C$21*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*('Supuestos'!$C$21*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="18">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="17">
         <f>RANK(E9,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6458,19 +6611,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*('Supuestos'!$C$23*1.1))*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*('Supuestos'!$C$23*1.1))*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*('Supuestos'!$C$23*1.1))*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="18">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="17">
         <f>RANK(E10,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6486,19 +6639,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*('Supuestos'!$C$24*1.1))*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*('Supuestos'!$C$24*1.1))-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*('Supuestos'!$C$24*1.1))*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="18">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="17">
         <f>RANK(E11,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6514,19 +6667,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*('Supuestos'!$C$25*1.1))*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*('Supuestos'!$C$25*1.1)))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="18">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="17">
         <f>RANK(E12,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6542,19 +6695,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*('Supuestos'!$C$28*1.1))+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="18">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="17">
         <f>RANK(E13,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6570,19 +6723,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-('Supuestos'!$C$34*0.9)-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="18">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>RANK(E14,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6590,10 +6743,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -6606,7 +6759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6626,87 +6779,94 @@
     <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Proyección a 12 meses y caja</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>La inversión crece cada mes según el supuesto de crecimiento. El cash entra según la curva de cobranza (mes 1 / 2 / 3). La ganancia acumulada muestra cuánto dinero hace falta para sostener la pauta.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Mes 3</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Mes 4</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Mes 5</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Mes 6</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Mes 7</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Mes 8</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Mes 9</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Mes 10</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Mes 11</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>Mes 12</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -6718,55 +6878,55 @@
           <t>Inversión en publicidad del mes</t>
         </is>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>'Supuestos'!$C$8*1</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>C6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>D6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>E6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <f>F6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="27">
         <f>G6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="27">
         <f>H6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="27">
         <f>I6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="27">
         <f>J6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="27">
         <f>K6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="27">
         <f>L6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="27">
         <f>M6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="9">
         <f>SUM(C6:N6)</f>
         <v/>
       </c>
@@ -6777,55 +6937,55 @@
           <t>Leads compradas</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>IF('Modelo'!$C$10=0,0,C6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="17">
         <f>IF('Modelo'!$C$10=0,0,D6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="17">
         <f>IF('Modelo'!$C$10=0,0,E6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="17">
         <f>IF('Modelo'!$C$10=0,0,F6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="17">
         <f>IF('Modelo'!$C$10=0,0,G6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="17">
         <f>IF('Modelo'!$C$10=0,0,H6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="17">
         <f>IF('Modelo'!$C$10=0,0,I6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="17">
         <f>IF('Modelo'!$C$10=0,0,J6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="17">
         <f>IF('Modelo'!$C$10=0,0,K6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="17">
         <f>IF('Modelo'!$C$10=0,0,L6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="17">
         <f>IF('Modelo'!$C$10=0,0,M6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="17">
         <f>IF('Modelo'!$C$10=0,0,N6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="12">
         <f>SUM(C7:N7)</f>
         <v/>
       </c>
@@ -6836,55 +6996,55 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <f>C7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <f>D7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>E7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <f>F7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <f>G7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <f>H7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="26">
         <f>I7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="26">
         <f>J7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="26">
         <f>K7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="26">
         <f>L7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="26">
         <f>M7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="26">
         <f>N7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="11">
         <f>SUM(C8:N8)</f>
         <v/>
       </c>
@@ -6895,55 +7055,55 @@
           <t>Facturado (todos los productos)</t>
         </is>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <f>C7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>D7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>E7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>F7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>G7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="27">
         <f>H7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="27">
         <f>I7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="27">
         <f>J7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="27">
         <f>K7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="27">
         <f>L7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="27">
         <f>M7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="27">
         <f>N7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="9">
         <f>SUM(C9:N9)</f>
         <v/>
       </c>
@@ -6954,55 +7114,55 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>C9*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>D9*'Supuestos'!$C$40+C9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>E9*'Supuestos'!$C$40+D9*'Supuestos'!$C$41+C9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>F9*'Supuestos'!$C$40+E9*'Supuestos'!$C$41+D9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <f>G9*'Supuestos'!$C$40+F9*'Supuestos'!$C$41+E9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="27">
         <f>H9*'Supuestos'!$C$40+G9*'Supuestos'!$C$41+F9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="27">
         <f>I9*'Supuestos'!$C$40+H9*'Supuestos'!$C$41+G9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="27">
         <f>J9*'Supuestos'!$C$40+I9*'Supuestos'!$C$41+H9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="27">
         <f>K9*'Supuestos'!$C$40+J9*'Supuestos'!$C$41+I9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="27">
         <f>L9*'Supuestos'!$C$40+K9*'Supuestos'!$C$41+J9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="27">
         <f>M9*'Supuestos'!$C$40+L9*'Supuestos'!$C$41+K9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="27">
         <f>N9*'Supuestos'!$C$40+M9*'Supuestos'!$C$41+L9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="9">
         <f>SUM(C10:N10)</f>
         <v/>
       </c>
@@ -7013,55 +7173,55 @@
           <t>Comisiones y reembolsos</t>
         </is>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>C10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>D10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>E10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>F10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="27">
         <f>G10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="27">
         <f>H10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="27">
         <f>I10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="27">
         <f>J10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="27">
         <f>K10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="27">
         <f>L10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="27">
         <f>M10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="27">
         <f>N10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="9">
         <f>SUM(C11:N11)</f>
         <v/>
       </c>
@@ -7072,55 +7232,55 @@
           <t>Costos por unidad (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>C7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>D7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>E7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>F7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>G7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="27">
         <f>H7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="27">
         <f>I7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="27">
         <f>J7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="27">
         <f>K7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="27">
         <f>L7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="27">
         <f>M7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="27">
         <f>N7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="9">
         <f>SUM(C12:N12)</f>
         <v/>
       </c>
@@ -7131,169 +7291,169 @@
           <t>Costos fijos del mes</t>
         </is>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="27">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="9">
         <f>SUM(C13:N13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja del mes</t>
         </is>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <f>C10-C11-C12-C13-C6</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f>D10-D11-D12-D13-D6</f>
         <v/>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <f>E10-E11-E12-E13-E6</f>
         <v/>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <f>F10-F11-F12-F13-F6</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <f>G10-G11-G12-G13-G6</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>H10-H11-H12-H13-H6</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f>I10-I11-I12-I13-I6</f>
         <v/>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="9">
         <f>J10-J11-J12-J13-J6</f>
         <v/>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="9">
         <f>K10-K11-K12-K13-K6</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="9">
         <f>L10-L11-L12-L13-L6</f>
         <v/>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="9">
         <f>M10-M11-M12-M13-M6</f>
         <v/>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="9">
         <f>N10-N11-N12-N13-N6</f>
         <v/>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="9">
         <f>SUM(C14:N14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja acumulada (desde cero)</t>
         </is>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="9">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>C15+D14</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <f>D15+E14</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <f>E15+F14</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <f>F15+G14</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <f>G15+H14</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <f>H15+I14</f>
         <v/>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="9">
         <f>I15+J14</f>
         <v/>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="9">
         <f>J15+K14</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="9">
         <f>K15+L14</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="9">
         <f>L15+M14</f>
         <v/>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="9">
         <f>M15+N14</f>
         <v/>
       </c>
@@ -7304,84 +7464,84 @@
           <t>Saldo de caja (caja inicial + ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <f>'Supuestos'!$C$49+C15</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <f>'Supuestos'!$C$49+D15</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <f>'Supuestos'!$C$49+E15</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="27">
         <f>'Supuestos'!$C$49+F15</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="27">
         <f>'Supuestos'!$C$49+G15</f>
         <v/>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="27">
         <f>'Supuestos'!$C$49+H15</f>
         <v/>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="27">
         <f>'Supuestos'!$C$49+I15</f>
         <v/>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="27">
         <f>'Supuestos'!$C$49+J15</f>
         <v/>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="27">
         <f>'Supuestos'!$C$49+K15</f>
         <v/>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="27">
         <f>'Supuestos'!$C$49+L15</f>
         <v/>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="27">
         <f>'Supuestos'!$C$49+M15</f>
         <v/>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="27">
         <f>'Supuestos'!$C$49+N15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Caja necesaria para no frenar la pauta (el peor momento de la ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <f>MAX(0,-MIN(C15:N15))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Saldo mínimo de caja con tu caja inicial</t>
         </is>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <f>MIN(C16:N16)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja acumulada en 12 meses</t>
         </is>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="9">
         <f>O14</f>
         <v/>
       </c>
@@ -7401,10 +7561,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -7417,7 +7577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7439,120 +7599,127 @@
     <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Seguimiento: una columna por mes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cargá los datos reales en las celdas amarillas. El semáforo compara tu costo real por lead con el techo móvil (lo que rindieron tus últimas 4 columnas) y con el techo del modelo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Dato</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Mes 3</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Mes 4</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Mes 5</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Mes 6</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Mes 7</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Mes 8</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Mes 9</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Mes 10</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Mes 11</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>Mes 12</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>Promedio</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>Máximo</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>Mínimo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Datos que cargás</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -7560,33 +7727,33 @@
           <t>Inversión en publicidad</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="22" t="n">
         <v>4500</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="22" t="n">
         <v>4800</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="22" t="n">
         <v>5200</v>
       </c>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="26">
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="27">
         <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
         <v/>
       </c>
-      <c r="P7" s="26">
+      <c r="P7" s="27">
         <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
         <v/>
       </c>
-      <c r="Q7" s="26">
+      <c r="Q7" s="27">
         <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
         <v/>
       </c>
@@ -7597,33 +7764,33 @@
           <t>Leads</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="21" t="n">
         <v>1600</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <v>1650</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <v>1900</v>
       </c>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="16">
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="17">
         <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
         <v/>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="17">
         <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
         <v/>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="17">
         <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
         <v/>
       </c>
@@ -7634,33 +7801,33 @@
           <t>Aplicaciones completas</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="21" t="n">
         <v>160</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <v>155</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <v>190</v>
       </c>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="16">
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="21" t="n"/>
+      <c r="O9" s="17">
         <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
         <v/>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="17">
         <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
         <v/>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="17">
         <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
         <v/>
       </c>
@@ -7671,33 +7838,33 @@
           <t>Calificados</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="21" t="n">
         <v>96</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <v>90</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <v>115</v>
       </c>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-      <c r="K10" s="20" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="20" t="n"/>
-      <c r="O10" s="16">
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
+      <c r="M10" s="21" t="n"/>
+      <c r="N10" s="21" t="n"/>
+      <c r="O10" s="17">
         <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
         <v/>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="17">
         <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
         <v/>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="17">
         <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
         <v/>
       </c>
@@ -7708,33 +7875,33 @@
           <t>Agendas</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>58</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="16">
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="21" t="n"/>
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="21" t="n"/>
+      <c r="O11" s="17">
         <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
         <v/>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="17">
         <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
         <v/>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="17">
         <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
         <v/>
       </c>
@@ -7745,33 +7912,33 @@
           <t>Llamadas realizadas</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>35</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="16">
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="21" t="n"/>
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="21" t="n"/>
+      <c r="O12" s="17">
         <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
         <v/>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="17">
         <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
         <v/>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="17">
         <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
         <v/>
       </c>
@@ -7782,33 +7949,33 @@
           <t>Ventas del programa</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="20" t="n"/>
-      <c r="O13" s="16">
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="21" t="n"/>
+      <c r="J13" s="21" t="n"/>
+      <c r="K13" s="21" t="n"/>
+      <c r="L13" s="21" t="n"/>
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="21" t="n"/>
+      <c r="O13" s="17">
         <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
         <v/>
       </c>
-      <c r="P13" s="16">
+      <c r="P13" s="17">
         <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
         <v/>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="17">
         <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
         <v/>
       </c>
@@ -7819,33 +7986,33 @@
           <t>Ventas del downsell</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="20" t="n"/>
-      <c r="O14" s="16">
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="21" t="n"/>
+      <c r="L14" s="21" t="n"/>
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="21" t="n"/>
+      <c r="O14" s="17">
         <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
         <v/>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="17">
         <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
         <v/>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q14" s="17">
         <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
         <v/>
       </c>
@@ -7856,33 +8023,33 @@
           <t>Facturado del mes (a precio de lista, con cuotas por cobrar)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="22" t="n">
         <v>16500</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="22" t="n">
         <v>13500</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="22" t="n">
         <v>21000</v>
       </c>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="26">
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="27">
         <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
         <v/>
       </c>
-      <c r="P15" s="26">
+      <c r="P15" s="27">
         <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
         <v/>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="27">
         <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
         <v/>
       </c>
@@ -7893,119 +8060,119 @@
           <t>Cash cobrado en el mes (incluye cuotas de meses anteriores)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="22" t="n">
         <v>9000</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="22" t="n">
         <v>11500</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="22" t="n">
         <v>15000</v>
       </c>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="26">
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="27">
         <f>IF(COUNT(C16:N16)=0,"",AVERAGE(C16:N16))</f>
         <v/>
       </c>
-      <c r="P16" s="26">
+      <c r="P16" s="27">
         <f>IF(COUNT(C16:N16)=0,"",MAX(C16:N16))</f>
         <v/>
       </c>
-      <c r="Q16" s="26">
+      <c r="Q16" s="27">
         <f>IF(COUNT(C16:N16)=0,"",MIN(C16:N16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Lo que calcula el modelo</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>CPL real</t>
         </is>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="13">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C8=0,0,C7/C8))</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="13">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D8=0,0,D7/D8))</f>
         <v/>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="13">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E8=0,0,E7/E8))</f>
         <v/>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F8=0,0,F7/F8))</f>
         <v/>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G8=0,0,G7/G8))</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H8=0,0,H7/H8))</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I8=0,0,I7/I8))</f>
         <v/>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="13">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J8=0,0,J7/J8))</f>
         <v/>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="13">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K8=0,0,K7/K8))</f>
         <v/>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="13">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L8=0,0,L7/L8))</f>
         <v/>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="13">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M8=0,0,M7/M8))</f>
         <v/>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="13">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N8=0,0,N7/N8))</f>
         <v/>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="20">
         <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
         <v/>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="20">
         <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
         <v/>
       </c>
-      <c r="Q18" s="19">
+      <c r="Q18" s="20">
         <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
         <v/>
       </c>
@@ -8016,63 +8183,63 @@
           <t>% lead → aplicación</t>
         </is>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C8=0,0,C9/C8))</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="18">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D8=0,0,D9/D8))</f>
         <v/>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="18">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E8=0,0,E9/E8))</f>
         <v/>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="18">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F8=0,0,F9/F8))</f>
         <v/>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="18">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G8=0,0,G9/G8))</f>
         <v/>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="18">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H8=0,0,H9/H8))</f>
         <v/>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="18">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I8=0,0,I9/I8))</f>
         <v/>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="18">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J8=0,0,J9/J8))</f>
         <v/>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="18">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K8=0,0,K9/K8))</f>
         <v/>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="18">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L8=0,0,L9/L8))</f>
         <v/>
       </c>
-      <c r="M19" s="17">
+      <c r="M19" s="18">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M8=0,0,M9/M8))</f>
         <v/>
       </c>
-      <c r="N19" s="17">
+      <c r="N19" s="18">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N8=0,0,N9/N8))</f>
         <v/>
       </c>
-      <c r="O19" s="17">
+      <c r="O19" s="18">
         <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
         <v/>
       </c>
-      <c r="P19" s="17">
+      <c r="P19" s="18">
         <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
         <v/>
       </c>
-      <c r="Q19" s="17">
+      <c r="Q19" s="18">
         <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
         <v/>
       </c>
@@ -8083,63 +8250,63 @@
           <t>% calificado → agenda</t>
         </is>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="18">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C10=0,0,C11/C10))</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="18">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D10=0,0,D11/D10))</f>
         <v/>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="18">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E10=0,0,E11/E10))</f>
         <v/>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="18">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F10=0,0,F11/F10))</f>
         <v/>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="18">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G10=0,0,G11/G10))</f>
         <v/>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="18">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H10=0,0,H11/H10))</f>
         <v/>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="18">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I10=0,0,I11/I10))</f>
         <v/>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="18">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J10=0,0,J11/J10))</f>
         <v/>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="18">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K10=0,0,K11/K10))</f>
         <v/>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="18">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L10=0,0,L11/L10))</f>
         <v/>
       </c>
-      <c r="M20" s="17">
+      <c r="M20" s="18">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M10=0,0,M11/M10))</f>
         <v/>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="18">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N10=0,0,N11/N10))</f>
         <v/>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="18">
         <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
         <v/>
       </c>
-      <c r="P20" s="17">
+      <c r="P20" s="18">
         <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
         <v/>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q20" s="18">
         <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
         <v/>
       </c>
@@ -8150,130 +8317,130 @@
           <t>% agenda → llamada (show)</t>
         </is>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="18">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C11=0,0,C12/C11))</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D11=0,0,D12/D11))</f>
         <v/>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="18">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E11=0,0,E12/E11))</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="18">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F11=0,0,F12/F11))</f>
         <v/>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="18">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G11=0,0,G12/G11))</f>
         <v/>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="18">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H11=0,0,H12/H11))</f>
         <v/>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="18">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I11=0,0,I12/I11))</f>
         <v/>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="18">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J11=0,0,J12/J11))</f>
         <v/>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="18">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K11=0,0,K12/K11))</f>
         <v/>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="18">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L11=0,0,L12/L11))</f>
         <v/>
       </c>
-      <c r="M21" s="17">
+      <c r="M21" s="18">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M11=0,0,M12/M11))</f>
         <v/>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N11=0,0,N12/N11))</f>
         <v/>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
         <v/>
       </c>
-      <c r="P21" s="17">
+      <c r="P21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
         <v/>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>% llamada → venta (cierre)</t>
         </is>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="36">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C12=0,0,C13/C12))</f>
         <v/>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="36">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D12=0,0,D13/D12))</f>
         <v/>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="36">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E12=0,0,E13/E12))</f>
         <v/>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="36">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F12=0,0,F13/F12))</f>
         <v/>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="36">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G12=0,0,G13/G12))</f>
         <v/>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="36">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H12=0,0,H13/H12))</f>
         <v/>
       </c>
-      <c r="I22" s="35">
+      <c r="I22" s="36">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I12=0,0,I13/I12))</f>
         <v/>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="36">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J12=0,0,J13/J12))</f>
         <v/>
       </c>
-      <c r="K22" s="35">
+      <c r="K22" s="36">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K12=0,0,K13/K12))</f>
         <v/>
       </c>
-      <c r="L22" s="35">
+      <c r="L22" s="36">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L12=0,0,L13/L12))</f>
         <v/>
       </c>
-      <c r="M22" s="35">
+      <c r="M22" s="36">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M12=0,0,M13/M12))</f>
         <v/>
       </c>
-      <c r="N22" s="35">
+      <c r="N22" s="36">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N12=0,0,N13/N12))</f>
         <v/>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="18">
         <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
         <v/>
       </c>
-      <c r="P22" s="17">
+      <c r="P22" s="18">
         <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
         <v/>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22" s="18">
         <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
         <v/>
       </c>
@@ -8284,63 +8451,63 @@
           <t>Costo por agenda</t>
         </is>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="20">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C11=0,0,C7/C11))</f>
         <v/>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D11=0,0,D7/D11))</f>
         <v/>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E11=0,0,E7/E11))</f>
         <v/>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F11=0,0,F7/F11))</f>
         <v/>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="20">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G11=0,0,G7/G11))</f>
         <v/>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="20">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H11=0,0,H7/H11))</f>
         <v/>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="20">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I11=0,0,I7/I11))</f>
         <v/>
       </c>
-      <c r="J23" s="19">
+      <c r="J23" s="20">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J11=0,0,J7/J11))</f>
         <v/>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="20">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K11=0,0,K7/K11))</f>
         <v/>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="20">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L11=0,0,L7/L11))</f>
         <v/>
       </c>
-      <c r="M23" s="19">
+      <c r="M23" s="20">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M11=0,0,M7/M11))</f>
         <v/>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="20">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N11=0,0,N7/N11))</f>
         <v/>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="20">
         <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
         <v/>
       </c>
-      <c r="P23" s="19">
+      <c r="P23" s="20">
         <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
         <v/>
       </c>
-      <c r="Q23" s="19">
+      <c r="Q23" s="20">
         <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
         <v/>
       </c>
@@ -8351,197 +8518,197 @@
           <t>CAC real</t>
         </is>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C13=0,0,C7/C13))</f>
         <v/>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D13=0,0,D7/D13))</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E13=0,0,E7/E13))</f>
         <v/>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F13=0,0,F7/F13))</f>
         <v/>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G13=0,0,G7/G13))</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H13=0,0,H7/H13))</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I13=0,0,I7/I13))</f>
         <v/>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="20">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J13=0,0,J7/J13))</f>
         <v/>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="20">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K13=0,0,K7/K13))</f>
         <v/>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="20">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L13=0,0,L7/L13))</f>
         <v/>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="20">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M13=0,0,M7/M13))</f>
         <v/>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="20">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N13=0,0,N7/N13))</f>
         <v/>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="20">
         <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
         <v/>
       </c>
-      <c r="P24" s="19">
+      <c r="P24" s="20">
         <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
         <v/>
       </c>
-      <c r="Q24" s="19">
+      <c r="Q24" s="20">
         <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Valor neto por unidad real (sobre facturado, cobranza completa)</t>
         </is>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="13">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C8=0,0,(C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36)/C8))</f>
         <v/>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="13">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D8=0,0,(D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36)/D8))</f>
         <v/>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="13">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E8=0,0,(E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36)/E8))</f>
         <v/>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="13">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F8=0,0,(F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36)/F8))</f>
         <v/>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="13">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G8=0,0,(G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36)/G8))</f>
         <v/>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="13">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H8=0,0,(H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36)/H8))</f>
         <v/>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="13">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I8=0,0,(I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36)/I8))</f>
         <v/>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="13">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J8=0,0,(J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36)/J8))</f>
         <v/>
       </c>
-      <c r="K25" s="12">
+      <c r="K25" s="13">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K8=0,0,(K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36)/K8))</f>
         <v/>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="13">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L8=0,0,(L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36)/L8))</f>
         <v/>
       </c>
-      <c r="M25" s="12">
+      <c r="M25" s="13">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M8=0,0,(M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36)/M8))</f>
         <v/>
       </c>
-      <c r="N25" s="12">
+      <c r="N25" s="13">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N8=0,0,(N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36)/N8))</f>
         <v/>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="20">
         <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
         <v/>
       </c>
-      <c r="P25" s="19">
+      <c r="P25" s="20">
         <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
         <v/>
       </c>
-      <c r="Q25" s="19">
+      <c r="Q25" s="20">
         <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período al completar la cobranza</t>
         </is>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="9">
         <f>IF(COUNT(C7:C16)&lt;10,"",C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
         <v/>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="9">
         <f>IF(COUNT(D7:D16)&lt;10,"",D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
         <v/>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="9">
         <f>IF(COUNT(E7:E16)&lt;10,"",E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
         <v/>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="9">
         <f>IF(COUNT(F7:F16)&lt;10,"",F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
         <v/>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="9">
         <f>IF(COUNT(G7:G16)&lt;10,"",G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
         <v/>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="9">
         <f>IF(COUNT(H7:H16)&lt;10,"",H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
         <v/>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="9">
         <f>IF(COUNT(I7:I16)&lt;10,"",I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
         <v/>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="9">
         <f>IF(COUNT(J7:J16)&lt;10,"",J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
         <v/>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="9">
         <f>IF(COUNT(K7:K16)&lt;10,"",K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
         <v/>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="9">
         <f>IF(COUNT(L7:L16)&lt;10,"",L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
         <v/>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="9">
         <f>IF(COUNT(M7:M16)&lt;10,"",M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
         <v/>
       </c>
-      <c r="N26" s="8">
+      <c r="N26" s="9">
         <f>IF(COUNT(N7:N16)&lt;10,"",N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
         <v/>
       </c>
-      <c r="O26" s="26">
+      <c r="O26" s="27">
         <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
         <v/>
       </c>
-      <c r="P26" s="26">
+      <c r="P26" s="27">
         <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
         <v/>
       </c>
-      <c r="Q26" s="26">
+      <c r="Q26" s="27">
         <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
         <v/>
       </c>
@@ -8552,197 +8719,197 @@
           <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="27">
         <f>IF(COUNT(C7:C16)&lt;10,"",C16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
         <v/>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="27">
         <f>IF(COUNT(D7:D16)&lt;10,"",D16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
         <v/>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="27">
         <f>IF(COUNT(E7:E16)&lt;10,"",E16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
         <v/>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="27">
         <f>IF(COUNT(F7:F16)&lt;10,"",F16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
         <v/>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="27">
         <f>IF(COUNT(G7:G16)&lt;10,"",G16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
         <v/>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="27">
         <f>IF(COUNT(H7:H16)&lt;10,"",H16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
         <v/>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="27">
         <f>IF(COUNT(I7:I16)&lt;10,"",I16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
         <v/>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="27">
         <f>IF(COUNT(J7:J16)&lt;10,"",J16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
         <v/>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="27">
         <f>IF(COUNT(K7:K16)&lt;10,"",K16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
         <v/>
       </c>
-      <c r="L27" s="26">
+      <c r="L27" s="27">
         <f>IF(COUNT(L7:L16)&lt;10,"",L16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
         <v/>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="27">
         <f>IF(COUNT(M7:M16)&lt;10,"",M16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
         <v/>
       </c>
-      <c r="N27" s="26">
+      <c r="N27" s="27">
         <f>IF(COUNT(N7:N16)&lt;10,"",N16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
         <v/>
       </c>
-      <c r="O27" s="26">
+      <c r="O27" s="27">
         <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
         <v/>
       </c>
-      <c r="P27" s="26">
+      <c r="P27" s="27">
         <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
         <v/>
       </c>
-      <c r="Q27" s="26">
+      <c r="Q27" s="27">
         <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Ganancia por unidad real (ganancia ÷ unidades)</t>
         </is>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="13">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C8=0,0,(C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)/C8))</f>
         <v/>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="13">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D8=0,0,(D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)/D8))</f>
         <v/>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="13">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E8=0,0,(E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)/E8))</f>
         <v/>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="13">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F8=0,0,(F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)/F8))</f>
         <v/>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="13">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G8=0,0,(G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)/G8))</f>
         <v/>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="13">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H8=0,0,(H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)/H8))</f>
         <v/>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="13">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I8=0,0,(I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)/I8))</f>
         <v/>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="13">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J8=0,0,(J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)/J8))</f>
         <v/>
       </c>
-      <c r="K28" s="12">
+      <c r="K28" s="13">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K8=0,0,(K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)/K8))</f>
         <v/>
       </c>
-      <c r="L28" s="12">
+      <c r="L28" s="13">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L8=0,0,(L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)/L8))</f>
         <v/>
       </c>
-      <c r="M28" s="12">
+      <c r="M28" s="13">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M8=0,0,(M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)/M8))</f>
         <v/>
       </c>
-      <c r="N28" s="12">
+      <c r="N28" s="13">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N8=0,0,(N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)/N8))</f>
         <v/>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="20">
         <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
         <v/>
       </c>
-      <c r="P28" s="19">
+      <c r="P28" s="20">
         <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
         <v/>
       </c>
-      <c r="Q28" s="19">
+      <c r="Q28" s="20">
         <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto (cobranza completa)</t>
         </is>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="10">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C7=0,0,C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
         <v/>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="10">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D7=0,0,D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
         <v/>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="10">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E7=0,0,E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
         <v/>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="10">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F7=0,0,F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
         <v/>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="10">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G7=0,0,G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
         <v/>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="10">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H7=0,0,H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="10">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I7=0,0,I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
         <v/>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="10">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J7=0,0,J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
         <v/>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="10">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K7=0,0,K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
         <v/>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="10">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L7=0,0,L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
         <v/>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="10">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M7=0,0,M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
         <v/>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="10">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N7=0,0,N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
         <v/>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="28">
         <f>IF(COUNT(C29:N29)=0,"",AVERAGE(C29:N29))</f>
         <v/>
       </c>
-      <c r="P29" s="27">
+      <c r="P29" s="28">
         <f>IF(COUNT(C29:N29)=0,"",MAX(C29:N29))</f>
         <v/>
       </c>
-      <c r="Q29" s="27">
+      <c r="Q29" s="28">
         <f>IF(COUNT(C29:N29)=0,"",MIN(C29:N29))</f>
         <v/>
       </c>
@@ -8753,63 +8920,63 @@
           <t>ROAS de caja (cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="28">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C7=0,0,C16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D7=0,0,D16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E7=0,0,E16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
         <v/>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="28">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F7=0,0,F16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
         <v/>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="28">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G7=0,0,G16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
         <v/>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="28">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H7=0,0,H16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
         <v/>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="28">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I7=0,0,I16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
         <v/>
       </c>
-      <c r="J30" s="27">
+      <c r="J30" s="28">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J7=0,0,J16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
         <v/>
       </c>
-      <c r="K30" s="27">
+      <c r="K30" s="28">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K7=0,0,K16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
         <v/>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="28">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L7=0,0,L16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
         <v/>
       </c>
-      <c r="M30" s="27">
+      <c r="M30" s="28">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M7=0,0,M16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
         <v/>
       </c>
-      <c r="N30" s="27">
+      <c r="N30" s="28">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N7=0,0,N16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
         <v/>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="28">
         <f>IF(COUNT(C30:N30)=0,"",AVERAGE(C30:N30))</f>
         <v/>
       </c>
-      <c r="P30" s="27">
+      <c r="P30" s="28">
         <f>IF(COUNT(C30:N30)=0,"",MAX(C30:N30))</f>
         <v/>
       </c>
-      <c r="Q30" s="27">
+      <c r="Q30" s="28">
         <f>IF(COUNT(C30:N30)=0,"",MIN(C30:N30))</f>
         <v/>
       </c>
@@ -8820,118 +8987,118 @@
           <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
         </is>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="20">
         <f>IF(COUNT(C7:C16)&lt;10,"",'Modelo'!$C$48)</f>
         <v/>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="20">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(COUNT(C25:C25)&gt;0,MEDIAN(C25:C25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="20">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(COUNT(C25:D25)&gt;0,MEDIAN(C25:D25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="20">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(COUNT(C25:E25)&gt;0,MEDIAN(C25:E25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="20">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(COUNT(C25:F25)&gt;0,MEDIAN(C25:F25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="20">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(COUNT(D25:G25)&gt;0,MEDIAN(D25:G25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="20">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(COUNT(E25:H25)&gt;0,MEDIAN(E25:H25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="J31" s="19">
+      <c r="J31" s="20">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(COUNT(F25:I25)&gt;0,MEDIAN(F25:I25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="K31" s="19">
+      <c r="K31" s="20">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(COUNT(G25:J25)&gt;0,MEDIAN(G25:J25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="20">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(COUNT(H25:K25)&gt;0,MEDIAN(H25:K25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="M31" s="19">
+      <c r="M31" s="20">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(COUNT(I25:L25)&gt;0,MEDIAN(I25:L25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="20">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(COUNT(J25:M25)&gt;0,MEDIAN(J25:M25),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="20">
         <f>IF(COUNT(C31:N31)=0,"",AVERAGE(C31:N31))</f>
         <v/>
       </c>
-      <c r="P31" s="19">
+      <c r="P31" s="20">
         <f>IF(COUNT(C31:N31)=0,"",MAX(C31:N31))</f>
         <v/>
       </c>
-      <c r="Q31" s="19">
+      <c r="Q31" s="20">
         <f>IF(COUNT(C31:N31)=0,"",MIN(C31:N31))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Semáforo (costo por unidad contra el techo móvil, y ROAS contra el objetivo)</t>
         </is>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="14">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C18&gt;C31,"ROJO",IF(AND(C18&lt;=C31/(1+'Supuestos'!$C$46),C29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="14">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D18&gt;D31,"ROJO",IF(AND(D18&lt;=D31/(1+'Supuestos'!$C$46),D29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="14">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E18&gt;E31,"ROJO",IF(AND(E18&lt;=E31/(1+'Supuestos'!$C$46),E29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="14">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F18&gt;F31,"ROJO",IF(AND(F18&lt;=F31/(1+'Supuestos'!$C$46),F29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="14">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G18&gt;G31,"ROJO",IF(AND(G18&lt;=G31/(1+'Supuestos'!$C$46),G29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="H32" s="13">
+      <c r="H32" s="14">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H18&gt;H31,"ROJO",IF(AND(H18&lt;=H31/(1+'Supuestos'!$C$46),H29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="I32" s="13">
+      <c r="I32" s="14">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I18&gt;I31,"ROJO",IF(AND(I18&lt;=I31/(1+'Supuestos'!$C$46),I29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="J32" s="13">
+      <c r="J32" s="14">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J18&gt;J31,"ROJO",IF(AND(J18&lt;=J31/(1+'Supuestos'!$C$46),J29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="K32" s="13">
+      <c r="K32" s="14">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K18&gt;K31,"ROJO",IF(AND(K18&lt;=K31/(1+'Supuestos'!$C$46),K29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="L32" s="13">
+      <c r="L32" s="14">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L18&gt;L31,"ROJO",IF(AND(L18&lt;=L31/(1+'Supuestos'!$C$46),L29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="M32" s="13">
+      <c r="M32" s="14">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M18&gt;M31,"ROJO",IF(AND(M18&lt;=M31/(1+'Supuestos'!$C$46),M29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="N32" s="13">
+      <c r="N32" s="14">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N18&gt;N31,"ROJO",IF(AND(N18&lt;=N31/(1+'Supuestos'!$C$46),N29&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
@@ -8950,10 +9117,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>

--- a/excel/03_Modelo_Financiero_Embudo_de_Llamada.xlsx
+++ b/excel/03_Modelo_Financiero_Embudo_de_Llamada.xlsx
@@ -180,6 +180,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,7 +199,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1065,33 +1065,33 @@
           <t>Inversión en publicidad</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="20" t="n">
         <v>4500</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>4800</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="20" t="n">
         <v>5200</v>
       </c>
-      <c r="F7" s="19" t="n"/>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="19" t="n"/>
-      <c r="I7" s="19" t="n"/>
-      <c r="J7" s="19" t="n"/>
-      <c r="K7" s="19" t="n"/>
-      <c r="L7" s="19" t="n"/>
-      <c r="M7" s="19" t="n"/>
-      <c r="N7" s="19" t="n"/>
-      <c r="O7" s="20">
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="20" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="L7" s="20" t="n"/>
+      <c r="M7" s="20" t="n"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="21">
         <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
         <v/>
       </c>
-      <c r="P7" s="20">
+      <c r="P7" s="21">
         <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
         <v/>
       </c>
-      <c r="Q7" s="20">
+      <c r="Q7" s="21">
         <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
         <v/>
       </c>
@@ -1102,33 +1102,33 @@
           <t>Leads</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="25" t="n">
         <v>1600</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="25" t="n">
         <v>1650</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="25" t="n">
         <v>1900</v>
       </c>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-      <c r="I8" s="24" t="n"/>
-      <c r="J8" s="24" t="n"/>
-      <c r="K8" s="24" t="n"/>
-      <c r="L8" s="24" t="n"/>
-      <c r="M8" s="24" t="n"/>
-      <c r="N8" s="24" t="n"/>
-      <c r="O8" s="21">
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="L8" s="25" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="25" t="n"/>
+      <c r="O8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
         <v/>
       </c>
-      <c r="P8" s="21">
+      <c r="P8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
         <v/>
       </c>
-      <c r="Q8" s="21">
+      <c r="Q8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
         <v/>
       </c>
@@ -1139,33 +1139,33 @@
           <t>Aplicaciones completas</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="25" t="n">
         <v>155</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="25" t="n">
         <v>190</v>
       </c>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="24" t="n"/>
-      <c r="K9" s="24" t="n"/>
-      <c r="L9" s="24" t="n"/>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="24" t="n"/>
-      <c r="O9" s="21">
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="25" t="n"/>
+      <c r="L9" s="25" t="n"/>
+      <c r="M9" s="25" t="n"/>
+      <c r="N9" s="25" t="n"/>
+      <c r="O9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
         <v/>
       </c>
-      <c r="P9" s="21">
+      <c r="P9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
         <v/>
       </c>
-      <c r="Q9" s="21">
+      <c r="Q9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
         <v/>
       </c>
@@ -1176,33 +1176,33 @@
           <t>Calificados</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="25" t="n">
         <v>96</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="25" t="n">
         <v>115</v>
       </c>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
-      <c r="J10" s="24" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="24" t="n"/>
-      <c r="M10" s="24" t="n"/>
-      <c r="N10" s="24" t="n"/>
-      <c r="O10" s="21">
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="25" t="n"/>
+      <c r="L10" s="25" t="n"/>
+      <c r="M10" s="25" t="n"/>
+      <c r="N10" s="25" t="n"/>
+      <c r="O10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
         <v/>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
         <v/>
       </c>
-      <c r="Q10" s="21">
+      <c r="Q10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
         <v/>
       </c>
@@ -1213,33 +1213,33 @@
           <t>Agendas</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="25" t="n">
         <v>58</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="25" t="n">
         <v>52</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="24" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="24" t="n"/>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="24" t="n"/>
-      <c r="O11" s="21">
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="25" t="n"/>
+      <c r="L11" s="25" t="n"/>
+      <c r="M11" s="25" t="n"/>
+      <c r="N11" s="25" t="n"/>
+      <c r="O11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
         <v/>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
         <v/>
       </c>
-      <c r="Q11" s="21">
+      <c r="Q11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
         <v/>
       </c>
@@ -1250,33 +1250,33 @@
           <t>Llamadas realizadas</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <v>41</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="24" t="n"/>
-      <c r="L12" s="24" t="n"/>
-      <c r="M12" s="24" t="n"/>
-      <c r="N12" s="24" t="n"/>
-      <c r="O12" s="21">
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="25" t="n"/>
+      <c r="M12" s="25" t="n"/>
+      <c r="N12" s="25" t="n"/>
+      <c r="O12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
         <v/>
       </c>
-      <c r="P12" s="21">
+      <c r="P12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
         <v/>
       </c>
-      <c r="Q12" s="21">
+      <c r="Q12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
         <v/>
       </c>
@@ -1287,33 +1287,33 @@
           <t>Ventas del programa</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="24" t="n"/>
-      <c r="K13" s="24" t="n"/>
-      <c r="L13" s="24" t="n"/>
-      <c r="M13" s="24" t="n"/>
-      <c r="N13" s="24" t="n"/>
-      <c r="O13" s="21">
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="25" t="n"/>
+      <c r="M13" s="25" t="n"/>
+      <c r="N13" s="25" t="n"/>
+      <c r="O13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
         <v/>
       </c>
-      <c r="P13" s="21">
+      <c r="P13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
         <v/>
       </c>
-      <c r="Q13" s="21">
+      <c r="Q13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
         <v/>
       </c>
@@ -1324,33 +1324,33 @@
           <t>Ventas del downsell</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="24" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="24" t="n"/>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="24" t="n"/>
-      <c r="K14" s="24" t="n"/>
-      <c r="L14" s="24" t="n"/>
-      <c r="M14" s="24" t="n"/>
-      <c r="N14" s="24" t="n"/>
-      <c r="O14" s="21">
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="25" t="n"/>
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="25" t="n"/>
+      <c r="O14" s="22">
         <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
         <v/>
       </c>
-      <c r="P14" s="21">
+      <c r="P14" s="22">
         <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
         <v/>
       </c>
-      <c r="Q14" s="21">
+      <c r="Q14" s="22">
         <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
         <v/>
       </c>
@@ -1361,33 +1361,33 @@
           <t>Facturado del mes (a precio de lista, con cuotas por cobrar)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="20" t="n">
         <v>16500</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="20" t="n">
         <v>13500</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="20" t="n">
         <v>21000</v>
       </c>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="19" t="n"/>
-      <c r="N15" s="19" t="n"/>
-      <c r="O15" s="20">
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="20" t="n"/>
+      <c r="M15" s="20" t="n"/>
+      <c r="N15" s="20" t="n"/>
+      <c r="O15" s="21">
         <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
         <v/>
       </c>
-      <c r="P15" s="20">
+      <c r="P15" s="21">
         <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
         <v/>
       </c>
-      <c r="Q15" s="20">
+      <c r="Q15" s="21">
         <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
         <v/>
       </c>
@@ -1398,33 +1398,33 @@
           <t>Cash cobrado en el mes (incluye cuotas de meses anteriores)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="20" t="n">
         <v>9000</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="20" t="n">
         <v>11500</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="20" t="n">
         <v>15000</v>
       </c>
-      <c r="F16" s="19" t="n"/>
-      <c r="G16" s="19" t="n"/>
-      <c r="H16" s="19" t="n"/>
-      <c r="I16" s="19" t="n"/>
-      <c r="J16" s="19" t="n"/>
-      <c r="K16" s="19" t="n"/>
-      <c r="L16" s="19" t="n"/>
-      <c r="M16" s="19" t="n"/>
-      <c r="N16" s="19" t="n"/>
-      <c r="O16" s="20">
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="20" t="n"/>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="20" t="n"/>
+      <c r="O16" s="21">
         <f>IF(COUNT(C16:N16)=0,"",AVERAGE(C16:N16))</f>
         <v/>
       </c>
-      <c r="P16" s="20">
+      <c r="P16" s="21">
         <f>IF(COUNT(C16:N16)=0,"",MAX(C16:N16))</f>
         <v/>
       </c>
-      <c r="Q16" s="20">
+      <c r="Q16" s="21">
         <f>IF(COUNT(C16:N16)=0,"",MIN(C16:N16))</f>
         <v/>
       </c>
@@ -1521,63 +1521,63 @@
           <t>% lead → aplicación</t>
         </is>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C8=0,0,C9/C8))</f>
         <v/>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D8=0,0,D9/D8))</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E8=0,0,E9/E8))</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="24">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F8=0,0,F9/F8))</f>
         <v/>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="24">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G8=0,0,G9/G8))</f>
         <v/>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="24">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H8=0,0,H9/H8))</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="24">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I8=0,0,I9/I8))</f>
         <v/>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="24">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J8=0,0,J9/J8))</f>
         <v/>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="24">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K8=0,0,K9/K8))</f>
         <v/>
       </c>
-      <c r="L19" s="23">
+      <c r="L19" s="24">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L8=0,0,L9/L8))</f>
         <v/>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="24">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M8=0,0,M9/M8))</f>
         <v/>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="24">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N8=0,0,N9/N8))</f>
         <v/>
       </c>
-      <c r="O19" s="23">
+      <c r="O19" s="24">
         <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
         <v/>
       </c>
-      <c r="P19" s="23">
+      <c r="P19" s="24">
         <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
         <v/>
       </c>
-      <c r="Q19" s="23">
+      <c r="Q19" s="24">
         <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
         <v/>
       </c>
@@ -1588,63 +1588,63 @@
           <t>% calificado → agenda</t>
         </is>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="24">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C10=0,0,C11/C10))</f>
         <v/>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="24">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D10=0,0,D11/D10))</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="24">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E10=0,0,E11/E10))</f>
         <v/>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="24">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F10=0,0,F11/F10))</f>
         <v/>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="24">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G10=0,0,G11/G10))</f>
         <v/>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="24">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H10=0,0,H11/H10))</f>
         <v/>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="24">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I10=0,0,I11/I10))</f>
         <v/>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="24">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J10=0,0,J11/J10))</f>
         <v/>
       </c>
-      <c r="K20" s="23">
+      <c r="K20" s="24">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K10=0,0,K11/K10))</f>
         <v/>
       </c>
-      <c r="L20" s="23">
+      <c r="L20" s="24">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L10=0,0,L11/L10))</f>
         <v/>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="24">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M10=0,0,M11/M10))</f>
         <v/>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="24">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N10=0,0,N11/N10))</f>
         <v/>
       </c>
-      <c r="O20" s="23">
+      <c r="O20" s="24">
         <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
         <v/>
       </c>
-      <c r="P20" s="23">
+      <c r="P20" s="24">
         <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
         <v/>
       </c>
-      <c r="Q20" s="23">
+      <c r="Q20" s="24">
         <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
         <v/>
       </c>
@@ -1655,63 +1655,63 @@
           <t>% agenda → llamada (show)</t>
         </is>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C11=0,0,C12/C11))</f>
         <v/>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="24">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D11=0,0,D12/D11))</f>
         <v/>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E11=0,0,E12/E11))</f>
         <v/>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="24">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F11=0,0,F12/F11))</f>
         <v/>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="24">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G11=0,0,G12/G11))</f>
         <v/>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="24">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H11=0,0,H12/H11))</f>
         <v/>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="24">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I11=0,0,I12/I11))</f>
         <v/>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="24">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J11=0,0,J12/J11))</f>
         <v/>
       </c>
-      <c r="K21" s="23">
+      <c r="K21" s="24">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K11=0,0,K12/K11))</f>
         <v/>
       </c>
-      <c r="L21" s="23">
+      <c r="L21" s="24">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L11=0,0,L12/L11))</f>
         <v/>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="24">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M11=0,0,M12/M11))</f>
         <v/>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="24">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N11=0,0,N12/N11))</f>
         <v/>
       </c>
-      <c r="O21" s="23">
+      <c r="O21" s="24">
         <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
         <v/>
       </c>
-      <c r="P21" s="23">
+      <c r="P21" s="24">
         <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
         <v/>
       </c>
-      <c r="Q21" s="23">
+      <c r="Q21" s="24">
         <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
         <v/>
       </c>
@@ -1722,63 +1722,63 @@
           <t>% llamada → venta (cierre)</t>
         </is>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="37">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C12=0,0,C13/C12))</f>
         <v/>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="37">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D12=0,0,D13/D12))</f>
         <v/>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="37">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E12=0,0,E13/E12))</f>
         <v/>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="37">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F12=0,0,F13/F12))</f>
         <v/>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="37">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G12=0,0,G13/G12))</f>
         <v/>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="37">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H12=0,0,H13/H12))</f>
         <v/>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="37">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I12=0,0,I13/I12))</f>
         <v/>
       </c>
-      <c r="J22" s="36">
+      <c r="J22" s="37">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J12=0,0,J13/J12))</f>
         <v/>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="37">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K12=0,0,K13/K12))</f>
         <v/>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="37">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L12=0,0,L13/L12))</f>
         <v/>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="37">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M12=0,0,M13/M12))</f>
         <v/>
       </c>
-      <c r="N22" s="36">
+      <c r="N22" s="37">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N12=0,0,N13/N12))</f>
         <v/>
       </c>
-      <c r="O22" s="23">
+      <c r="O22" s="24">
         <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
         <v/>
       </c>
-      <c r="P22" s="23">
+      <c r="P22" s="24">
         <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
         <v/>
       </c>
-      <c r="Q22" s="23">
+      <c r="Q22" s="24">
         <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
         <v/>
       </c>
@@ -2038,15 +2038,15 @@
         <f>IF(COUNT(N7:N16)&lt;10,"",N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
         <v/>
       </c>
-      <c r="O26" s="20">
+      <c r="O26" s="21">
         <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
         <v/>
       </c>
-      <c r="P26" s="20">
+      <c r="P26" s="21">
         <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
         <v/>
       </c>
-      <c r="Q26" s="20">
+      <c r="Q26" s="21">
         <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
         <v/>
       </c>
@@ -2057,63 +2057,63 @@
           <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="21">
         <f>IF(COUNT(C7:C16)&lt;10,"",C16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
         <v/>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="21">
         <f>IF(COUNT(D7:D16)&lt;10,"",D16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
         <v/>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="21">
         <f>IF(COUNT(E7:E16)&lt;10,"",E16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
         <v/>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="21">
         <f>IF(COUNT(F7:F16)&lt;10,"",F16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
         <v/>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="21">
         <f>IF(COUNT(G7:G16)&lt;10,"",G16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
         <v/>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="21">
         <f>IF(COUNT(H7:H16)&lt;10,"",H16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
         <v/>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="21">
         <f>IF(COUNT(I7:I16)&lt;10,"",I16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
         <v/>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="21">
         <f>IF(COUNT(J7:J16)&lt;10,"",J16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
         <v/>
       </c>
-      <c r="K27" s="20">
+      <c r="K27" s="21">
         <f>IF(COUNT(K7:K16)&lt;10,"",K16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
         <v/>
       </c>
-      <c r="L27" s="20">
+      <c r="L27" s="21">
         <f>IF(COUNT(L7:L16)&lt;10,"",L16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
         <v/>
       </c>
-      <c r="M27" s="20">
+      <c r="M27" s="21">
         <f>IF(COUNT(M7:M16)&lt;10,"",M16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
         <v/>
       </c>
-      <c r="N27" s="20">
+      <c r="N27" s="21">
         <f>IF(COUNT(N7:N16)&lt;10,"",N16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
         <v/>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="21">
         <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
         <v/>
       </c>
-      <c r="P27" s="20">
+      <c r="P27" s="21">
         <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
         <v/>
       </c>
-      <c r="Q27" s="20">
+      <c r="Q27" s="21">
         <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
         <v/>
       </c>
@@ -2239,15 +2239,15 @@
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N7=0,0,N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
         <v/>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="28">
         <f>IF(COUNT(C29:N29)=0,"",AVERAGE(C29:N29))</f>
         <v/>
       </c>
-      <c r="P29" s="27">
+      <c r="P29" s="28">
         <f>IF(COUNT(C29:N29)=0,"",MAX(C29:N29))</f>
         <v/>
       </c>
-      <c r="Q29" s="27">
+      <c r="Q29" s="28">
         <f>IF(COUNT(C29:N29)=0,"",MIN(C29:N29))</f>
         <v/>
       </c>
@@ -2258,63 +2258,63 @@
           <t>ROAS de caja (cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="28">
         <f>IF(COUNT(C7:C16)&lt;10,"",IF(C7=0,0,C16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(COUNT(D7:D16)&lt;10,"",IF(D7=0,0,D16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(COUNT(E7:E16)&lt;10,"",IF(E7=0,0,E16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
         <v/>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="28">
         <f>IF(COUNT(F7:F16)&lt;10,"",IF(F7=0,0,F16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
         <v/>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="28">
         <f>IF(COUNT(G7:G16)&lt;10,"",IF(G7=0,0,G16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
         <v/>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="28">
         <f>IF(COUNT(H7:H16)&lt;10,"",IF(H7=0,0,H16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
         <v/>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="28">
         <f>IF(COUNT(I7:I16)&lt;10,"",IF(I7=0,0,I16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
         <v/>
       </c>
-      <c r="J30" s="27">
+      <c r="J30" s="28">
         <f>IF(COUNT(J7:J16)&lt;10,"",IF(J7=0,0,J16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
         <v/>
       </c>
-      <c r="K30" s="27">
+      <c r="K30" s="28">
         <f>IF(COUNT(K7:K16)&lt;10,"",IF(K7=0,0,K16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
         <v/>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="28">
         <f>IF(COUNT(L7:L16)&lt;10,"",IF(L7=0,0,L16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
         <v/>
       </c>
-      <c r="M30" s="27">
+      <c r="M30" s="28">
         <f>IF(COUNT(M7:M16)&lt;10,"",IF(M7=0,0,M16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
         <v/>
       </c>
-      <c r="N30" s="27">
+      <c r="N30" s="28">
         <f>IF(COUNT(N7:N16)&lt;10,"",IF(N7=0,0,N16*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
         <v/>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="28">
         <f>IF(COUNT(C30:N30)=0,"",AVERAGE(C30:N30))</f>
         <v/>
       </c>
-      <c r="P30" s="27">
+      <c r="P30" s="28">
         <f>IF(COUNT(C30:N30)=0,"",MAX(C30:N30))</f>
         <v/>
       </c>
-      <c r="Q30" s="27">
+      <c r="Q30" s="28">
         <f>IF(COUNT(C30:N30)=0,"",MIN(C30:N30))</f>
         <v/>
       </c>
@@ -2604,7 +2604,7 @@
           <t>&gt;18 %</t>
         </is>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="24">
         <f>'Supuestos'!$C$21</f>
         <v/>
       </c>
@@ -2640,7 +2640,7 @@
           <t>&gt;70 %</t>
         </is>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="24">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -2676,7 +2676,7 @@
           <t>&gt;70 %</t>
         </is>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="24">
         <f>'Supuestos'!$C$23</f>
         <v/>
       </c>
@@ -2712,7 +2712,7 @@
           <t>&gt;75 %</t>
         </is>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="24">
         <f>'Supuestos'!$C$24</f>
         <v/>
       </c>
@@ -2748,7 +2748,7 @@
           <t>&gt;35 %</t>
         </is>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="24">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -2784,7 +2784,7 @@
           <t>&gt;1,5 %</t>
         </is>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
@@ -2856,7 +2856,7 @@
           <t>&gt;2,5</t>
         </is>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="28">
         <f>'Modelo'!$C$45</f>
         <v/>
       </c>
@@ -3597,7 +3597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3650,7 +3650,7 @@
           <t>Ninguna celda con error en Modelo</t>
         </is>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="19">
         <f>IF(ISERROR(SUM('Modelo'!C5:C160)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3666,7 +3666,7 @@
           <t>Ninguna celda con error en Simulador</t>
         </is>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="19">
         <f>IF(ISERROR(SUM('Simulador'!C5:G220)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3682,7 +3682,7 @@
           <t>Ninguna celda con error en Embudo</t>
         </is>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="19">
         <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3698,7 +3698,7 @@
           <t>Ninguna celda con error en Resumen</t>
         </is>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="19">
         <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3714,7 +3714,7 @@
           <t>Ninguna celda con error en Proyección 12 meses</t>
         </is>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="19">
         <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3730,7 +3730,7 @@
           <t>Ninguna celda con error en Escenarios</t>
         </is>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="19">
         <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3746,7 +3746,7 @@
           <t>Ninguna celda con error en Seguimiento</t>
         </is>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="19">
         <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3762,7 +3762,7 @@
           <t>Los supuestos de tráfico son mayores a cero</t>
         </is>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="19">
         <f>IF(AND('Supuestos'!$C$9&gt;0,'Supuestos'!$C$10&gt;0,'Supuestos'!$C$11&gt;0,'Supuestos'!$C$14&gt;0),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3778,7 +3778,7 @@
           <t>La curva de cobranza suma 100 %</t>
         </is>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="19">
         <f>IF(ABS('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42-1)&lt;0.001,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3794,7 +3794,7 @@
           <t>Comisiones + reembolsos menores al 60 %</t>
         </is>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="19">
         <f>IF(('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)&lt;0.6,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3810,7 +3810,7 @@
           <t>El escenario en uso es 1, 2 o 3</t>
         </is>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="19">
         <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3826,7 +3826,7 @@
           <t>La inversión es mayor a cero</t>
         </is>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="19">
         <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3838,7 +3838,7 @@
           <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
         </is>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="19">
         <f>IF('Modelo'!$C$25&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3854,7 +3854,7 @@
           <t>Las conversiones están entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="19">
         <f>IF(AND('Supuestos'!$C$10&gt;=0,'Supuestos'!$C$10&lt;=1,'Supuestos'!$C$11&gt;=0,'Supuestos'!$C$11&lt;=1,'Supuestos'!$C$14&gt;=0,'Supuestos'!$C$14&lt;=1,'Supuestos'!$C$18&gt;=0,'Supuestos'!$C$18&lt;=1,'Supuestos'!$C$21&gt;=0,'Supuestos'!$C$21&lt;=1,'Supuestos'!$C$22&gt;=0,'Supuestos'!$C$22&lt;=1,'Supuestos'!$C$23&gt;=0,'Supuestos'!$C$23&lt;=1,'Supuestos'!$C$24&gt;=0,'Supuestos'!$C$24&lt;=1,'Supuestos'!$C$25&gt;=0,'Supuestos'!$C$25&lt;=1,'Supuestos'!$C$30&gt;=0,'Supuestos'!$C$30&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3870,7 +3870,7 @@
           <t>El margen de seguridad está entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="19">
         <f>IF(AND('Supuestos'!$C$46&gt;=0,'Supuestos'!$C$46&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3882,7 +3882,7 @@
           <t>El crecimiento mensual está entre −50 % y 100 %</t>
         </is>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="19">
         <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3898,7 +3898,7 @@
           <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
         </is>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="19">
         <f>IF(AND('Modelo'!$C$15&lt;='Modelo'!$C$11,'Modelo'!$C$16&lt;='Modelo'!$C$15,'Modelo'!$C$17&lt;='Modelo'!$C$16,'Modelo'!$C$18&lt;='Modelo'!$C$17,'Modelo'!$C$23&lt;='Modelo'!$C$18),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3914,7 +3914,7 @@
           <t>El interruptor de evento previo es 0 o 1</t>
         </is>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="19">
         <f>IF(OR('Supuestos'!$C$17=0,'Supuestos'!$C$17=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3924,19 +3924,212 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Simulador: lo que escribiste en las celdas amarillas</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+    </row>
     <row r="25">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ningún supuesto del Simulador fuera de rango (porcentajes entre 0 y 1, números no negativos)</t>
+        </is>
+      </c>
+      <c r="C25" s="19">
+        <f>IF(COUNTIF('Simulador'!$I$6:$I$93,"REVISAR")=0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>La columna Rango del Simulador marca la fila con el problema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Simulador: Los supuestos de tráfico son mayores a cero</t>
+        </is>
+      </c>
+      <c r="C26" s="19">
+        <f>IF(AND('Simulador'!$C$7&gt;0,'Simulador'!$C$10&gt;0,'Simulador'!$C$12&gt;0,'Simulador'!$C$14&gt;0),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Simulador: La curva de cobranza suma 100 %</t>
+        </is>
+      </c>
+      <c r="C27" s="19">
+        <f>IF(ABS('Simulador'!$C$49+'Simulador'!$C$50+'Simulador'!$C$51-1)&lt;0.001,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Simulador: Comisiones + reembolsos menores al 60 %</t>
+        </is>
+      </c>
+      <c r="C28" s="19">
+        <f>IF(('Simulador'!$C$54+'Simulador'!$C$55+'Simulador'!$C$57)&lt;0.6,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Si suman más, revisá los porcentajes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Simulador: El escenario en uso es 1, 2 o 3</t>
+        </is>
+      </c>
+      <c r="C29" s="19">
+        <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Supuestos → celda 'Escenario en uso'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Simulador: La inversión es mayor a cero</t>
+        </is>
+      </c>
+      <c r="C30" s="19">
+        <f>IF('Simulador'!$C$8&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Simulador: La meta de ventas es alcanzable (hay conversión a venta)</t>
+        </is>
+      </c>
+      <c r="C31" s="19">
+        <f>IF('Simulador'!$E$38&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Simulador: Las conversiones están entre 0 y 100 %</t>
+        </is>
+      </c>
+      <c r="C32" s="19">
+        <f>IF(AND('Simulador'!$C$10&gt;=0,'Simulador'!$C$10&lt;=1,'Simulador'!$C$12&gt;=0,'Simulador'!$C$12&lt;=1,'Simulador'!$C$14&gt;=0,'Simulador'!$C$14&lt;=1,'Simulador'!$C$19&gt;=0,'Simulador'!$C$19&lt;=1,'Simulador'!$C$22&gt;=0,'Simulador'!$C$22&lt;=1,'Simulador'!$C$24&gt;=0,'Simulador'!$C$24&lt;=1,'Simulador'!$C$26&gt;=0,'Simulador'!$C$26&lt;=1,'Simulador'!$C$28&gt;=0,'Simulador'!$C$28&lt;=1,'Simulador'!$C$34&gt;=0,'Simulador'!$C$34&lt;=1,'Simulador'!$C$36&gt;=0,'Simulador'!$C$36&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Simulador: El margen de seguridad está entre 0 y 100 %</t>
+        </is>
+      </c>
+      <c r="C33" s="19">
+        <f>IF(AND('Simulador'!$C$73&gt;=0,'Simulador'!$C$73&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Simulador: El crecimiento mensual está entre −50 % y 100 %</t>
+        </is>
+      </c>
+      <c r="C34" s="19">
+        <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Más de 100 % por mes no es realista para una proyección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Simulador: La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
+        </is>
+      </c>
+      <c r="C35" s="19">
+        <f>IF(AND('Simulador'!$E$23&lt;='Simulador'!$E$16,'Simulador'!$E$25&lt;='Simulador'!$E$23,'Simulador'!$E$27&lt;='Simulador'!$E$25,'Simulador'!$E$29&lt;='Simulador'!$E$27,'Simulador'!$E$35&lt;='Simulador'!$E$29),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Si falla, alguna conversión está por encima de 100 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Simulador: El interruptor de evento previo es 0 o 1</t>
+        </is>
+      </c>
+      <c r="C36" s="19">
+        <f>IF(OR('Simulador'!$C$18=0,'Simulador'!$C$18=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Supuestos → evento previo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Estado general del modelo</t>
         </is>
       </c>
-      <c r="C25" s="38">
-        <f>IF(COUNTIF(C6:C23,"REVISAR")=0,"OK","REVISAR")</f>
+      <c r="C38" s="38">
+        <f>IF(COUNTIF(C6:C36,"REVISAR")=0,"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:C25">
+  <conditionalFormatting sqref="C6:C38">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4612,7 +4805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4623,6 +4816,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4680,6 +4874,11 @@
       <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Rango</t>
         </is>
       </c>
     </row>
@@ -4719,6 +4918,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I7" s="19">
+        <f>IF(AND(ISNUMBER(C7),C7&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -4726,11 +4929,11 @@
           <t>Inversión en publicidad por mes</t>
         </is>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <f>'Supuestos'!$C$8</f>
         <v/>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <f>'Supuestos'!$C$8</f>
         <v/>
       </c>
@@ -4743,6 +4946,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I8" s="19">
+        <f>IF(AND(ISNUMBER(C8),C8&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -4750,15 +4957,15 @@
           <t>Impresiones</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="22">
         <f>IF($C$7=0,0,$C$8/$C$7*1000)</f>
         <v/>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="22">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="22">
         <f>IF(AND(ISNUMBER(E9),ISNUMBER(F9)),E9-F9,"")</f>
         <v/>
       </c>
@@ -4774,11 +4981,11 @@
           <t>CTR al enlace</t>
         </is>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>'Supuestos'!$C$10</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
         <f>'Supuestos'!$C$10</f>
         <v/>
       </c>
@@ -4791,6 +4998,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I10" s="19">
+        <f>IF(AND(ISNUMBER(C10),C10&gt;=0,C10&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -4798,15 +5009,15 @@
           <t>Clics al enlace</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="22">
         <f>$E$9*$C$10</f>
         <v/>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="22">
         <f>IF(AND(ISNUMBER(E11),ISNUMBER(F11)),E11-F11,"")</f>
         <v/>
       </c>
@@ -4822,11 +5033,11 @@
           <t>% de clics que cargan la página</t>
         </is>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="23">
         <f>'Supuestos'!$C$11</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
         <f>'Supuestos'!$C$11</f>
         <v/>
       </c>
@@ -4839,6 +5050,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I12" s="19">
+        <f>IF(AND(ISNUMBER(C12),C12&gt;=0,C12&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -4846,15 +5061,15 @@
           <t>Visitas a la página</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="22">
         <f>$E$11*$C$12</f>
         <v/>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="22">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="22">
         <f>IF(AND(ISNUMBER(E13),ISNUMBER(F13)),E13-F13,"")</f>
         <v/>
       </c>
@@ -4870,11 +5085,11 @@
           <t>% de visitas que dejan sus datos (lead)</t>
         </is>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="23">
         <f>'Supuestos'!$C$14</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
         <f>'Supuestos'!$C$14</f>
         <v/>
       </c>
@@ -4887,6 +5102,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I14" s="19">
+        <f>IF(AND(ISNUMBER(C14),C14&gt;=0,C14&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
@@ -4922,11 +5141,11 @@
         <f>IF($E$15=0,0,$C$8/$E$15)</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="22">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="22">
         <f>IF(AND(ISNUMBER(E16),ISNUMBER(F16)),E16-F16,"")</f>
         <v/>
       </c>
@@ -4955,11 +5174,11 @@
           <t>¿Hay webinar o evento antes de la aplicación? (1 = sí, 0 = no)</t>
         </is>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="25">
         <f>'Supuestos'!$C$17</f>
         <v/>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="22">
         <f>'Supuestos'!$C$17</f>
         <v/>
       </c>
@@ -4972,6 +5191,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I18" s="19">
+        <f>IF(AND(ISNUMBER(C18),C18&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -4979,11 +5202,11 @@
           <t>% de leads que asisten al evento</t>
         </is>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="23">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -4996,6 +5219,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I19" s="19">
+        <f>IF(AND(ISNUMBER(C19),C19&gt;=0,C19&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -5003,15 +5230,15 @@
           <t>Asistentes al evento (si hay)</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="22">
         <f>IF($C$18=1,$E$16*$C$19,0)</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="22">
         <f>'Modelo'!$C$13</f>
         <v/>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="22">
         <f>IF(AND(ISNUMBER(E20),ISNUMBER(F20)),E20-F20,"")</f>
         <v/>
       </c>
@@ -5027,15 +5254,15 @@
           <t>Base de la aplicación (asistentes o leads)</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="22">
         <f>IF($C$18=1,$E$20,$E$16)</f>
         <v/>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="22">
         <f>'Modelo'!$C$14</f>
         <v/>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="22">
         <f>IF(AND(ISNUMBER(E21),ISNUMBER(F21)),E21-F21,"")</f>
         <v/>
       </c>
@@ -5051,11 +5278,11 @@
           <t>% que completa la aplicación (de leads, o de asistentes si hay evento)</t>
         </is>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="23">
         <f>'Supuestos'!$C$21</f>
         <v/>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="24">
         <f>'Supuestos'!$C$21</f>
         <v/>
       </c>
@@ -5068,6 +5295,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I22" s="19">
+        <f>IF(AND(ISNUMBER(C22),C22&gt;=0,C22&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -5075,15 +5306,15 @@
           <t>Aplicaciones completas</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="22">
         <f>$E$21*$C$22</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="22">
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="22">
         <f>IF(AND(ISNUMBER(E23),ISNUMBER(F23)),E23-F23,"")</f>
         <v/>
       </c>
@@ -5099,11 +5330,11 @@
           <t>% de aplicaciones que califican</t>
         </is>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="24">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -5116,6 +5347,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I24" s="19">
+        <f>IF(AND(ISNUMBER(C24),C24&gt;=0,C24&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -5123,15 +5358,15 @@
           <t>Calificados</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="22">
         <f>$E$23*$C$24</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="22">
         <f>'Modelo'!$C$16</f>
         <v/>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="22">
         <f>IF(AND(ISNUMBER(E25),ISNUMBER(F25)),E25-F25,"")</f>
         <v/>
       </c>
@@ -5147,11 +5382,11 @@
           <t>% de calificados que agendan</t>
         </is>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="23">
         <f>'Supuestos'!$C$23</f>
         <v/>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="24">
         <f>'Supuestos'!$C$23</f>
         <v/>
       </c>
@@ -5164,6 +5399,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I26" s="19">
+        <f>IF(AND(ISNUMBER(C26),C26&gt;=0,C26&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
@@ -5175,11 +5414,11 @@
         <f>$E$25*$C$26</f>
         <v/>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="26">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="26">
         <f>IF(AND(ISNUMBER(E27),ISNUMBER(F27)),E27-F27,"")</f>
         <v/>
       </c>
@@ -5195,11 +5434,11 @@
           <t>% de agendas que aparecen en la llamada</t>
         </is>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="23">
         <f>'Supuestos'!$C$24</f>
         <v/>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="24">
         <f>'Supuestos'!$C$24</f>
         <v/>
       </c>
@@ -5212,6 +5451,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I28" s="19">
+        <f>IF(AND(ISNUMBER(C28),C28&gt;=0,C28&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -5219,15 +5462,15 @@
           <t>Llamadas realizadas</t>
         </is>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="26">
         <f>$E$27*$C$28</f>
         <v/>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="26">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="26">
         <f>IF(AND(ISNUMBER(E29),ISNUMBER(F29)),E29-F29,"")</f>
         <v/>
       </c>
@@ -5328,11 +5571,11 @@
           <t>% de llamadas que compran</t>
         </is>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="23">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="24">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -5345,6 +5588,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I34" s="19">
+        <f>IF(AND(ISNUMBER(C34),C34&gt;=0,C34&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
@@ -5356,11 +5603,11 @@
         <f>$E$29*$C$34</f>
         <v/>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="26">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="26">
         <f>IF(AND(ISNUMBER(E35),ISNUMBER(F35)),E35-F35,"")</f>
         <v/>
       </c>
@@ -5376,11 +5623,11 @@
           <t>Downsell: % de los que no compraron que lo toman</t>
         </is>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="23">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="24">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -5393,6 +5640,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I36" s="19">
+        <f>IF(AND(ISNUMBER(C36),C36&gt;=0,C36&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
@@ -5400,15 +5651,15 @@
           <t>Ventas del downsell</t>
         </is>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="26">
         <f>($E$29-$E$35)*$C$36</f>
         <v/>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="26">
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="26">
         <f>IF(AND(ISNUMBER(E37),ISNUMBER(F37)),E37-F37,"")</f>
         <v/>
       </c>
@@ -5424,15 +5675,15 @@
           <t>% de leads que compran el programa</t>
         </is>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="27">
         <f>IF($E$16=0,0,$E$35/$E$16)</f>
         <v/>
       </c>
-      <c r="F38" s="26">
+      <c r="F38" s="27">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="G38" s="26">
+      <c r="G38" s="27">
         <f>IF(AND(ISNUMBER(E38),ISNUMBER(F38)),E38-F38,"")</f>
         <v/>
       </c>
@@ -5489,6 +5740,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I40" s="19">
+        <f>IF(AND(ISNUMBER(C40),C40&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
@@ -5496,15 +5751,15 @@
           <t>Facturado: programa</t>
         </is>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="21">
         <f>$E$35*$C$40</f>
         <v/>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="21">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="21">
         <f>IF(AND(ISNUMBER(E41),ISNUMBER(F41)),E41-F41,"")</f>
         <v/>
       </c>
@@ -5537,6 +5792,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I42" s="19">
+        <f>IF(AND(ISNUMBER(C42),C42&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -5544,15 +5803,15 @@
           <t>Facturado: downsell</t>
         </is>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="21">
         <f>$E$37*$C$42</f>
         <v/>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="21">
         <f>'Modelo'!$C$28</f>
         <v/>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="21">
         <f>IF(AND(ISNUMBER(E43),ISNUMBER(F43)),E43-F43,"")</f>
         <v/>
       </c>
@@ -5572,11 +5831,11 @@
         <f>$E$41+$E$43</f>
         <v/>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="21">
         <f>'Modelo'!$C$29</f>
         <v/>
       </c>
-      <c r="G44" s="20">
+      <c r="G44" s="21">
         <f>IF(AND(ISNUMBER(E44),ISNUMBER(F44)),E44-F44,"")</f>
         <v/>
       </c>
@@ -5616,15 +5875,15 @@
           <t>Ventas del programa por lead (para la proyección)</t>
         </is>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="27">
         <f>IF($E$16=0,0,$E$35/$E$16)</f>
         <v/>
       </c>
-      <c r="F46" s="26">
+      <c r="F46" s="27">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="G46" s="26">
+      <c r="G46" s="27">
         <f>IF(AND(ISNUMBER(E46),ISNUMBER(F46)),E46-F46,"")</f>
         <v/>
       </c>
@@ -5677,11 +5936,11 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="23">
         <f>'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="24">
         <f>'Supuestos'!$C$40</f>
         <v/>
       </c>
@@ -5694,6 +5953,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I49" s="19">
+        <f>IF(AND(ISNUMBER(C49),C49&gt;=0,C49&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
@@ -5701,11 +5964,11 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="23">
         <f>'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="D50" s="23">
+      <c r="D50" s="24">
         <f>'Supuestos'!$C$41</f>
         <v/>
       </c>
@@ -5718,6 +5981,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I50" s="19">
+        <f>IF(AND(ISNUMBER(C50),C50&gt;=0,C50&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -5725,11 +5992,11 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="23">
         <f>'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="24">
         <f>'Supuestos'!$C$42</f>
         <v/>
       </c>
@@ -5742,6 +6009,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I51" s="19">
+        <f>IF(AND(ISNUMBER(C51),C51&gt;=0,C51&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -5749,15 +6020,15 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="21">
         <f>$E$44*($C$49+$C$50+$C$51)</f>
         <v/>
       </c>
-      <c r="F52" s="20">
+      <c r="F52" s="21">
         <f>'Modelo'!$C$34</f>
         <v/>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="21">
         <f>IF(AND(ISNUMBER(E52),ISNUMBER(F52)),E52-F52,"")</f>
         <v/>
       </c>
@@ -5773,15 +6044,15 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="21">
         <f>$E$44*$C$49</f>
         <v/>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="21">
         <f>'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="G53" s="20">
+      <c r="G53" s="21">
         <f>IF(AND(ISNUMBER(E53),ISNUMBER(F53)),E53-F53,"")</f>
         <v/>
       </c>
@@ -5797,11 +6068,11 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="23">
         <f>'Supuestos'!$C$33</f>
         <v/>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="24">
         <f>'Supuestos'!$C$33</f>
         <v/>
       </c>
@@ -5814,6 +6085,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I54" s="19">
+        <f>IF(AND(ISNUMBER(C54),C54&gt;=0,C54&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -5821,11 +6096,11 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="23">
         <f>'Supuestos'!$C$34</f>
         <v/>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="24">
         <f>'Supuestos'!$C$34</f>
         <v/>
       </c>
@@ -5838,6 +6113,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I55" s="19">
+        <f>IF(AND(ISNUMBER(C55),C55&gt;=0,C55&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -5845,15 +6124,15 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="21">
         <f>$E$52*($C$54+$C$55)</f>
         <v/>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="21">
         <f>'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="G56" s="20">
+      <c r="G56" s="21">
         <f>IF(AND(ISNUMBER(E56),ISNUMBER(F56)),E56-F56,"")</f>
         <v/>
       </c>
@@ -5869,11 +6148,11 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C57" s="22">
+      <c r="C57" s="23">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="D57" s="23">
+      <c r="D57" s="24">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -5886,6 +6165,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I57" s="19">
+        <f>IF(AND(ISNUMBER(C57),C57&gt;=0,C57&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -5893,15 +6176,15 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="21">
         <f>$E$52*$C$57</f>
         <v/>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="21">
         <f>'Modelo'!$C$37</f>
         <v/>
       </c>
-      <c r="G58" s="20">
+      <c r="G58" s="21">
         <f>IF(AND(ISNUMBER(E58),ISNUMBER(F58)),E58-F58,"")</f>
         <v/>
       </c>
@@ -5921,11 +6204,11 @@
         <f>$E$52*(1-$C$54-$C$55-$C$57)</f>
         <v/>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="21">
         <f>'Modelo'!$C$38</f>
         <v/>
       </c>
-      <c r="G59" s="20">
+      <c r="G59" s="21">
         <f>IF(AND(ISNUMBER(E59),ISNUMBER(F59)),E59-F59,"")</f>
         <v/>
       </c>
@@ -5958,6 +6241,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I60" s="19">
+        <f>IF(AND(ISNUMBER(C60),C60&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -5965,15 +6252,15 @@
           <t>Costos por lead (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="E61" s="20">
+      <c r="E61" s="21">
         <f>$E$16*$C$60</f>
         <v/>
       </c>
-      <c r="F61" s="20">
+      <c r="F61" s="21">
         <f>'Modelo'!$C$39</f>
         <v/>
       </c>
-      <c r="G61" s="20">
+      <c r="G61" s="21">
         <f>IF(AND(ISNUMBER(E61),ISNUMBER(F61)),E61-F61,"")</f>
         <v/>
       </c>
@@ -5989,11 +6276,11 @@
           <t>Costos fijos por mes</t>
         </is>
       </c>
-      <c r="C62" s="19">
+      <c r="C62" s="20">
         <f>'Supuestos'!$C$37</f>
         <v/>
       </c>
-      <c r="D62" s="20">
+      <c r="D62" s="21">
         <f>'Supuestos'!$C$37</f>
         <v/>
       </c>
@@ -6006,6 +6293,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I62" s="19">
+        <f>IF(AND(ISNUMBER(C62),C62&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
@@ -6017,11 +6308,11 @@
         <f>$E$59-$E$61-$C$62-$C$8</f>
         <v/>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="21">
         <f>'Modelo'!$C$40</f>
         <v/>
       </c>
-      <c r="G63" s="20">
+      <c r="G63" s="21">
         <f>IF(AND(ISNUMBER(E63),ISNUMBER(F63)),E63-F63,"")</f>
         <v/>
       </c>
@@ -6037,15 +6328,15 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="E64" s="27">
+      <c r="E64" s="28">
         <f>IF($C$8=0,0,$E$44/$C$8)</f>
         <v/>
       </c>
-      <c r="F64" s="27">
+      <c r="F64" s="28">
         <f>'Modelo'!$C$41</f>
         <v/>
       </c>
-      <c r="G64" s="27">
+      <c r="G64" s="28">
         <f>IF(AND(ISNUMBER(E64),ISNUMBER(F64)),E64-F64,"")</f>
         <v/>
       </c>
@@ -6065,11 +6356,11 @@
         <f>IF($C$8=0,0,$E$59/$C$8)</f>
         <v/>
       </c>
-      <c r="F65" s="27">
+      <c r="F65" s="28">
         <f>'Modelo'!$C$42</f>
         <v/>
       </c>
-      <c r="G65" s="27">
+      <c r="G65" s="28">
         <f>IF(AND(ISNUMBER(E65),ISNUMBER(F65)),E65-F65,"")</f>
         <v/>
       </c>
@@ -6085,15 +6376,15 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="E66" s="23">
+      <c r="E66" s="24">
         <f>IF($E$52=0,0,$E$63/$E$52)</f>
         <v/>
       </c>
-      <c r="F66" s="23">
+      <c r="F66" s="24">
         <f>'Modelo'!$C$43</f>
         <v/>
       </c>
-      <c r="G66" s="23">
+      <c r="G66" s="24">
         <f>IF(AND(ISNUMBER(E66),ISNUMBER(F66)),E66-F66,"")</f>
         <v/>
       </c>
@@ -6109,11 +6400,11 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="29">
         <f>'Supuestos'!$C$45</f>
         <v/>
       </c>
-      <c r="D67" s="27">
+      <c r="D67" s="28">
         <f>'Supuestos'!$C$45</f>
         <v/>
       </c>
@@ -6126,6 +6417,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I67" s="19">
+        <f>IF(AND(ISNUMBER(C67),C67&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
@@ -6133,11 +6428,11 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="E68" s="29">
+      <c r="E68" s="30">
         <f>IF($E$65&gt;=$C$67,"SÍ","NO")</f>
         <v/>
       </c>
-      <c r="F68" s="29">
+      <c r="F68" s="30">
         <f>'Modelo'!$C$44</f>
         <v/>
       </c>
@@ -6161,11 +6456,11 @@
         <f>$E$53*(1-$C$54-$C$55-$C$57)/$C$8</f>
         <v/>
       </c>
-      <c r="F69" s="27">
+      <c r="F69" s="28">
         <f>'Modelo'!$C$45</f>
         <v/>
       </c>
-      <c r="G69" s="27">
+      <c r="G69" s="28">
         <f>IF(AND(ISNUMBER(E69),ISNUMBER(F69)),E69-F69,"")</f>
         <v/>
       </c>
@@ -6242,11 +6537,11 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="23">
         <f>'Supuestos'!$C$46</f>
         <v/>
       </c>
-      <c r="D73" s="23">
+      <c r="D73" s="24">
         <f>'Supuestos'!$C$46</f>
         <v/>
       </c>
@@ -6258,6 +6553,10 @@
         <is>
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
+      </c>
+      <c r="I73" s="19">
+        <f>IF(AND(ISNUMBER(C73),C73&gt;=0,C73&lt;=1),"OK","REVISAR")</f>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -6427,7 +6726,7 @@
         <f>IF($E$15&gt;$E$72,"ROJO",IF(AND($E$15&lt;=$E$74,$E$65&gt;=$C$67),"VERDE","AMARILLO"))</f>
         <v/>
       </c>
-      <c r="F81" s="29">
+      <c r="F81" s="30">
         <f>'Modelo'!$C$56</f>
         <v/>
       </c>
@@ -6447,11 +6746,11 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C82" s="24">
+      <c r="C82" s="25">
         <f>'Supuestos'!$C$47</f>
         <v/>
       </c>
-      <c r="D82" s="21">
+      <c r="D82" s="22">
         <f>'Supuestos'!$C$47</f>
         <v/>
       </c>
@@ -6464,6 +6763,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I82" s="19">
+        <f>IF(AND(ISNUMBER(C82),C82&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="4" t="inlineStr">
@@ -6475,11 +6778,11 @@
         <f>IF($E$38=0,"inalcanzable con estos supuestos",$C$82/$E$38*$E$15)</f>
         <v/>
       </c>
-      <c r="F83" s="20">
+      <c r="F83" s="21">
         <f>'Modelo'!$C$57</f>
         <v/>
       </c>
-      <c r="G83" s="20">
+      <c r="G83" s="21">
         <f>IF(AND(ISNUMBER(E83),ISNUMBER(F83)),E83-F83,"")</f>
         <v/>
       </c>
@@ -6495,15 +6798,15 @@
           <t>Inversión para la meta al CPL objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="E84" s="20">
+      <c r="E84" s="21">
         <f>IF($E$38=0,"inalcanzable con estos supuestos",$C$82/$E$38*$E$74)</f>
         <v/>
       </c>
-      <c r="F84" s="20">
+      <c r="F84" s="21">
         <f>'Modelo'!$C$58</f>
         <v/>
       </c>
-      <c r="G84" s="20">
+      <c r="G84" s="21">
         <f>IF(AND(ISNUMBER(E84),ISNUMBER(F84)),E84-F84,"")</f>
         <v/>
       </c>
@@ -6519,15 +6822,15 @@
           <t>Llamadas que hay que atender por mes para esa meta</t>
         </is>
       </c>
-      <c r="E85" s="25">
+      <c r="E85" s="26">
         <f>IF($C$34=0,"inalcanzable con estos supuestos",$C$82/$C$34)</f>
         <v/>
       </c>
-      <c r="F85" s="25">
+      <c r="F85" s="26">
         <f>'Modelo'!$C$59</f>
         <v/>
       </c>
-      <c r="G85" s="25">
+      <c r="G85" s="26">
         <f>IF(AND(ISNUMBER(E85),ISNUMBER(F85)),E85-F85,"")</f>
         <v/>
       </c>
@@ -6739,39 +7042,61 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>La columna Rango avisa si escribiste algo imposible (un porcentaje fuera de 0 a 1, un negativo, texto) y Chequeos repite los chequeos del modelo con tus números del Simulador.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B98:H98"/>
     <mergeCell ref="B95:H95"/>
     <mergeCell ref="B96:H96"/>
   </mergeCells>
+  <conditionalFormatting sqref="I6:I93">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+      <formula>"REVISAR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C6:C93">
-    <cfRule type="expression" priority="1" dxfId="3">
+    <cfRule type="expression" priority="2" dxfId="3">
       <formula>AND(ISNUMBER(C6),C6&lt;&gt;D6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E68:F68">
-    <cfRule type="expression" priority="2" dxfId="0">
+    <cfRule type="expression" priority="3" dxfId="0">
       <formula>LEFT(E68,5)="VERDE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>LEFT(E68,8)="AMARILLO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
+    <cfRule type="expression" priority="5" dxfId="2">
       <formula>LEFT(E68,4)="ROJO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E81:F81">
-    <cfRule type="expression" priority="5" dxfId="0">
+    <cfRule type="expression" priority="6" dxfId="0">
       <formula>LEFT(E81,5)="VERDE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="1">
       <formula>LEFT(E81,8)="AMARILLO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="2">
       <formula>LEFT(E81,4)="ROJO"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C10 C12 C14 C19 C22 C24 C26 C28 C34 C36 C49 C50 C51 C54 C55 C57 C73" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Porcentaje fuera de rango" error="Escribí el porcentaje como fracción entre 0 y 1 (15 % = 0,15)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C7 C8 C18 C40 C42 C60 C62 C67 C82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Tiene que ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
@@ -6873,7 +7198,7 @@
           <t>Impresiones del anuncio (por mil)</t>
         </is>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="22">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
@@ -6911,11 +7236,11 @@
           <t>Clics al enlace</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="24">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$8/'Modelo'!$C$7)</f>
         <v/>
       </c>
@@ -6948,11 +7273,11 @@
           <t>Visitas a la página</t>
         </is>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="24">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6985,15 +7310,15 @@
           <t>Leads</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="22">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="24">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$11/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -7021,15 +7346,15 @@
           <t>Asisten al evento previo (si hay)</t>
         </is>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="22">
         <f>'Modelo'!$C$13</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$13/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$13/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -7057,15 +7382,15 @@
           <t>Completan la aplicación</t>
         </is>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="24">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$15/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$15/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -7093,15 +7418,15 @@
           <t>Califican</t>
         </is>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="22">
         <f>'Modelo'!$C$16</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
         <f>IF('Modelo'!$C$15=0,0,'Modelo'!$C$16/'Modelo'!$C$15)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$16/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -7129,15 +7454,15 @@
           <t>Agendan la llamada</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="22">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$17/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$17/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -7165,15 +7490,15 @@
           <t>Aparecen en la llamada (show)</t>
         </is>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
         <f>IF('Modelo'!$C$17=0,0,'Modelo'!$C$18/'Modelo'!$C$17)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$18/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -7201,15 +7526,15 @@
           <t>Compran el programa</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$23/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -7237,15 +7562,15 @@
           <t>Toman el downsell</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="24">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$24/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$24/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -7447,7 +7772,7 @@
           <t>Escenario en uso (1 = conservador · 2 = base · 3 = optimista)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="25" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -7480,7 +7805,7 @@
           <t>Inversión en publicidad por mes</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>4500</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -7530,17 +7855,17 @@
           <t>CTR al enlace</t>
         </is>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="24">
         <f>IF('Supuestos'!$C$6=1,D10,IF('Supuestos'!$C$6=2,E10,F10))</f>
         <v/>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>0.012</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <v>0.015</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <v>0.02</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -7556,7 +7881,7 @@
           <t>% de clics que cargan la página</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>0.85</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -7585,17 +7910,17 @@
           <t>% de visitas que dejan sus datos (lead)</t>
         </is>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="24">
         <f>IF('Supuestos'!$C$6=1,D14,IF('Supuestos'!$C$6=2,E14,F14))</f>
         <v/>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="23" t="n">
         <v>0.28</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>0.35</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -7628,7 +7953,7 @@
           <t>¿Hay webinar o evento antes de la aplicación? (1 = sí, 0 = no)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="25" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -7648,17 +7973,17 @@
           <t>% de leads que asisten al evento</t>
         </is>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="24">
         <f>IF('Supuestos'!$C$6=1,D18,IF('Supuestos'!$C$6=2,E18,F18))</f>
         <v/>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="23" t="n">
         <v>0.14</v>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F18" s="23" t="n">
         <v>0.2</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -7691,17 +8016,17 @@
           <t>% que completa la aplicación (de leads, o de asistentes si hay evento)</t>
         </is>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <f>IF('Supuestos'!$C$6=1,D21,IF('Supuestos'!$C$6=2,E21,F21))</f>
         <v/>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="23" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="F21" s="22" t="n">
+      <c r="F21" s="23" t="n">
         <v>0.15</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -7721,17 +8046,17 @@
           <t>% de aplicaciones que califican</t>
         </is>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="24">
         <f>IF('Supuestos'!$C$6=1,D22,IF('Supuestos'!$C$6=2,E22,F22))</f>
         <v/>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="F22" s="22" t="n">
+      <c r="F22" s="23" t="n">
         <v>0.7</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -7751,17 +8076,17 @@
           <t>% de calificados que agendan</t>
         </is>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="24">
         <f>IF('Supuestos'!$C$6=1,D23,IF('Supuestos'!$C$6=2,E23,F23))</f>
         <v/>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="23" t="n">
         <v>0.45</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E23" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="F23" s="22" t="n">
+      <c r="F23" s="23" t="n">
         <v>0.75</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -7781,17 +8106,17 @@
           <t>% de agendas que aparecen en la llamada</t>
         </is>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="24">
         <f>IF('Supuestos'!$C$6=1,D24,IF('Supuestos'!$C$6=2,E24,F24))</f>
         <v/>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="E24" s="22" t="n">
+      <c r="E24" s="23" t="n">
         <v>0.7</v>
       </c>
-      <c r="F24" s="22" t="n">
+      <c r="F24" s="23" t="n">
         <v>0.8</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -7811,17 +8136,17 @@
           <t>% de llamadas que compran</t>
         </is>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="24">
         <f>IF('Supuestos'!$C$6=1,D25,IF('Supuestos'!$C$6=2,E25,F25))</f>
         <v/>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="E25" s="22" t="n">
+      <c r="E25" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="F25" s="22" t="n">
+      <c r="F25" s="23" t="n">
         <v>0.35</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -7894,17 +8219,17 @@
           <t>Downsell: % de los que no compraron que lo toman</t>
         </is>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="24">
         <f>IF('Supuestos'!$C$6=1,D30,IF('Supuestos'!$C$6=2,E30,F30))</f>
         <v/>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="F30" s="22" t="n">
+      <c r="F30" s="23" t="n">
         <v>0.15</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -7933,7 +8258,7 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -7953,7 +8278,7 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -7973,7 +8298,7 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C35" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -8013,7 +8338,7 @@
           <t>Costos fijos por mes</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n">
+      <c r="C37" s="20" t="n">
         <v>2500</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -8046,7 +8371,7 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C40" s="22" t="n">
+      <c r="C40" s="23" t="n">
         <v>0.6</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -8066,7 +8391,7 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C41" s="22" t="n">
+      <c r="C41" s="23" t="n">
         <v>0.2</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -8086,7 +8411,7 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C42" s="22" t="n">
+      <c r="C42" s="23" t="n">
         <v>0.2</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -8119,7 +8444,7 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C45" s="28" t="n">
+      <c r="C45" s="29" t="n">
         <v>2.5</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -8139,7 +8464,7 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n">
+      <c r="C46" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -8159,7 +8484,7 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C47" s="24" t="n">
+      <c r="C47" s="25" t="n">
         <v>15</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -8179,7 +8504,7 @@
           <t>Crecimiento de la inversión por mes (proyección)</t>
         </is>
       </c>
-      <c r="C48" s="22" t="n">
+      <c r="C48" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -8199,7 +8524,7 @@
           <t>Caja inicial</t>
         </is>
       </c>
-      <c r="C49" s="19" t="n">
+      <c r="C49" s="20" t="n">
         <v>8000</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -8294,7 +8619,7 @@
           <t>Impresiones</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>IF('Supuestos'!$C$9=0,0,'Supuestos'!$C$8/'Supuestos'!$C$9*1000)</f>
         <v/>
       </c>
@@ -8310,7 +8635,7 @@
           <t>Clics al enlace</t>
         </is>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <f>'Modelo'!$C$7*'Supuestos'!$C$10</f>
         <v/>
       </c>
@@ -8326,7 +8651,7 @@
           <t>Visitas a la página</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="22">
         <f>'Modelo'!$C$8*'Supuestos'!$C$11</f>
         <v/>
       </c>
@@ -8383,7 +8708,7 @@
           <t>Asistentes al evento (si hay)</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="22">
         <f>IF('Supuestos'!$C$17=1,'Modelo'!$C$11*'Supuestos'!$C$18,0)</f>
         <v/>
       </c>
@@ -8399,7 +8724,7 @@
           <t>Base de la aplicación (asistentes o leads)</t>
         </is>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>IF('Supuestos'!$C$17=1,'Modelo'!$C$13,'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -8415,7 +8740,7 @@
           <t>Aplicaciones completas</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <f>'Modelo'!$C$14*'Supuestos'!$C$21</f>
         <v/>
       </c>
@@ -8431,7 +8756,7 @@
           <t>Calificados</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <f>'Modelo'!$C$15*'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -8463,7 +8788,7 @@
           <t>Llamadas realizadas</t>
         </is>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <f>'Modelo'!$C$17*'Supuestos'!$C$24</f>
         <v/>
       </c>
@@ -8552,7 +8877,7 @@
           <t>Ventas del downsell</t>
         </is>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>('Modelo'!$C$18-'Modelo'!$C$23)*'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -8568,7 +8893,7 @@
           <t>% de leads que compran el programa</t>
         </is>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -8600,7 +8925,7 @@
           <t>Facturado: programa</t>
         </is>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="21">
         <f>'Modelo'!$C$23*'Supuestos'!$C$28</f>
         <v/>
       </c>
@@ -8616,7 +8941,7 @@
           <t>Facturado: downsell</t>
         </is>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="21">
         <f>'Modelo'!$C$24*'Supuestos'!$C$29</f>
         <v/>
       </c>
@@ -8664,7 +8989,7 @@
           <t>Ventas del programa por lead (para la proyección)</t>
         </is>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="27">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$23/'Modelo'!$C$11)</f>
         <v/>
       </c>
@@ -8705,7 +9030,7 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="21">
         <f>'Modelo'!$C$29*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42)</f>
         <v/>
       </c>
@@ -8721,7 +9046,7 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="21">
         <f>'Modelo'!$C$29*'Supuestos'!$C$40</f>
         <v/>
       </c>
@@ -8737,7 +9062,7 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="21">
         <f>'Modelo'!$C$34*('Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
@@ -8753,7 +9078,7 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="21">
         <f>'Modelo'!$C$34*'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -8785,7 +9110,7 @@
           <t>Costos por lead (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="21">
         <f>'Modelo'!$C$11*'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -8817,7 +9142,7 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="28">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$29/'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -8849,7 +9174,7 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C43" s="23">
+      <c r="C43" s="24">
         <f>IF('Modelo'!$C$34=0,0,'Modelo'!$C$40/'Modelo'!$C$34)</f>
         <v/>
       </c>
@@ -8865,7 +9190,7 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="30">
         <f>IF('Modelo'!$C$42&gt;='Supuestos'!$C$45,"SÍ","NO")</f>
         <v/>
       </c>
@@ -9075,7 +9400,7 @@
           <t>Inversión para la meta al CPL objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="21">
         <f>IF('Modelo'!$C$25=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Modelo'!$C$25*'Modelo'!$C$49)</f>
         <v/>
       </c>
@@ -9091,7 +9416,7 @@
           <t>Llamadas que hay que atender por mes para esa meta</t>
         </is>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="26">
         <f>IF('Supuestos'!$C$25=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Supuestos'!$C$25)</f>
         <v/>
       </c>
@@ -9295,7 +9620,7 @@
           <t>Umbral de 'cerca del cero' (inversión × margen de seguridad)</t>
         </is>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="21">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$46</f>
         <v/>
       </c>
@@ -9320,195 +9645,195 @@
           <t>Precio ↓  /  % cierre →</t>
         </is>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="H9" s="30" t="n">
+      <c r="H9" s="31" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>497</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B10)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <v>997</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B11)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="32" t="n">
         <v>1500</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B12)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <v>2500</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B13)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <v>3500</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B14)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="32" t="n">
         <v>5000</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9)*$B15)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$9))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -9533,224 +9858,224 @@
           <t>CPL ↓  /  % cierre →</t>
         </is>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G20" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="H20" s="30" t="n">
+      <c r="H20" s="31" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="32" t="n">
+      <c r="B21" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$18,0)),(IF($B21=0,0,'Supuestos'!$C$8/$B21))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="32" t="n">
+      <c r="B22" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$18,0)),(IF($B22=0,0,'Supuestos'!$C$8/$B22))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="32" t="n">
+      <c r="B23" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$18,0)),(IF($B23=0,0,'Supuestos'!$C$8/$B23))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="32" t="n">
+      <c r="B24" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$18,0)),(IF($B24=0,0,'Supuestos'!$C$8/$B24))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="32" t="n">
+      <c r="B25" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$18,0)),(IF($B25=0,0,'Supuestos'!$C$8/$B25))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="32" t="n">
+      <c r="B26" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$18,0)),(IF($B26=0,0,'Supuestos'!$C$8/$B26))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="32" t="n">
+      <c r="B27" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*C$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*D$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*E$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*F$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*G$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$18,0)),(IF($B27=0,0,'Supuestos'!$C$8/$B27))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*H$20))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B27=0,0,'Supuestos'!$C$8/$B27))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -9775,143 +10100,143 @@
           <t>Facturación objetivo ↓ / ROAS objetivo →</t>
         </is>
       </c>
-      <c r="C32" s="33" t="n">
+      <c r="C32" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="33" t="n">
+      <c r="D32" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="33" t="n">
+      <c r="E32" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="33" t="n">
+      <c r="F32" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G32" s="33" t="n">
+      <c r="G32" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="32" t="n">
         <v>20000</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="21">
         <f>$B33/C$32</f>
         <v/>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="21">
         <f>$B33/D$32</f>
         <v/>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="21">
         <f>$B33/E$32</f>
         <v/>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="21">
         <f>$B33/F$32</f>
         <v/>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="21">
         <f>$B33/G$32</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="32" t="n">
         <v>50000</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="21">
         <f>$B34/C$32</f>
         <v/>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="21">
         <f>$B34/D$32</f>
         <v/>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="21">
         <f>$B34/E$32</f>
         <v/>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="21">
         <f>$B34/F$32</f>
         <v/>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="21">
         <f>$B34/G$32</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="32" t="n">
         <v>100000</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="21">
         <f>$B35/C$32</f>
         <v/>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="21">
         <f>$B35/D$32</f>
         <v/>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="21">
         <f>$B35/E$32</f>
         <v/>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="21">
         <f>$B35/F$32</f>
         <v/>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="21">
         <f>$B35/G$32</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="31" t="n">
+      <c r="B36" s="32" t="n">
         <v>200000</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="21">
         <f>$B36/C$32</f>
         <v/>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="21">
         <f>$B36/D$32</f>
         <v/>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="21">
         <f>$B36/E$32</f>
         <v/>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="21">
         <f>$B36/F$32</f>
         <v/>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="21">
         <f>$B36/G$32</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="31" t="n">
+      <c r="B37" s="32" t="n">
         <v>500000</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="21">
         <f>$B37/C$32</f>
         <v/>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="21">
         <f>$B37/D$32</f>
         <v/>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="21">
         <f>$B37/E$32</f>
         <v/>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="21">
         <f>$B37/F$32</f>
         <v/>
       </c>
-      <c r="G37" s="20">
+      <c r="G37" s="21">
         <f>$B37/G$32</f>
         <v/>
       </c>
@@ -9924,51 +10249,51 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="34">
+      <c r="B39" s="35">
         <f>$B33</f>
         <v/>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="22">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B33/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="34">
+      <c r="B40" s="35">
         <f>$B34</f>
         <v/>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="22">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B34/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="34">
+      <c r="B41" s="35">
         <f>$B35</f>
         <v/>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="22">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B35/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="34">
+      <c r="B42" s="35">
         <f>$B36</f>
         <v/>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="22">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B36/'Modelo'!$C$32)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="34">
+      <c r="B43" s="35">
         <f>$B37</f>
         <v/>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="22">
         <f>IF('Modelo'!$C$32=0,"inalcanzable",$B37/'Modelo'!$C$32)</f>
         <v/>
       </c>
@@ -9981,19 +10306,19 @@
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="35" t="n">
+      <c r="C46" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="35" t="n">
+      <c r="D46" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="E46" s="35" t="n">
+      <c r="E46" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="35" t="n">
+      <c r="F46" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="35" t="n">
+      <c r="G46" s="36" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10073,15 +10398,15 @@
           <t>actual</t>
         </is>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="21">
         <f>'Supuestos'!$C$8*1.0</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="28">
         <f>IF(C54=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C54-'Supuestos'!$C$8))/C54)</f>
         <v/>
       </c>
-      <c r="E54" s="20">
+      <c r="E54" s="21">
         <f>C54*(D54-1)</f>
         <v/>
       </c>
@@ -10092,15 +10417,15 @@
           <t>× 1.25</t>
         </is>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="21">
         <f>'Supuestos'!$C$8*1.25</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="28">
         <f>IF(C55=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C55-'Supuestos'!$C$8))/C55)</f>
         <v/>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="21">
         <f>C55*(D55-1)</f>
         <v/>
       </c>
@@ -10111,15 +10436,15 @@
           <t>× 1.5</t>
         </is>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="21">
         <f>'Supuestos'!$C$8*1.5</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="28">
         <f>IF(C56=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C56-'Supuestos'!$C$8))/C56)</f>
         <v/>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="21">
         <f>C56*(D56-1)</f>
         <v/>
       </c>
@@ -10130,15 +10455,15 @@
           <t>× 2</t>
         </is>
       </c>
-      <c r="C57" s="20">
+      <c r="C57" s="21">
         <f>'Supuestos'!$C$8*2.0</f>
         <v/>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="28">
         <f>IF(C57=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C57-'Supuestos'!$C$8))/C57)</f>
         <v/>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="21">
         <f>C57*(D57-1)</f>
         <v/>
       </c>
@@ -10149,15 +10474,15 @@
           <t>× 3</t>
         </is>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="21">
         <f>'Supuestos'!$C$8*3.0</f>
         <v/>
       </c>
-      <c r="D58" s="27">
+      <c r="D58" s="28">
         <f>IF(C58=0,0,('Supuestos'!$C$8*'Modelo'!$C$42+1.3*(C58-'Supuestos'!$C$8))/C58)</f>
         <v/>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="21">
         <f>C58*(D58-1)</f>
         <v/>
       </c>
@@ -10292,19 +10617,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,('Supuestos'!$C$9*0.9)/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f>RANK(E7,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10320,19 +10645,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1)=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*('Supuestos'!$C$14*1.1))))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="22">
         <f>RANK(E8,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10348,19 +10673,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*('Supuestos'!$C$21*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*('Supuestos'!$C$21*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*('Supuestos'!$C$21*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="24">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="22">
         <f>RANK(E9,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10376,19 +10701,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*('Supuestos'!$C$23*1.1))*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*('Supuestos'!$C$23*1.1))*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*('Supuestos'!$C$23*1.1))*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="22">
         <f>RANK(E10,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10404,19 +10729,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*('Supuestos'!$C$24*1.1))*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*('Supuestos'!$C$24*1.1))-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*('Supuestos'!$C$24*1.1))*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="22">
         <f>RANK(E11,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10432,19 +10757,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*('Supuestos'!$C$25*1.1))*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*('Supuestos'!$C$25*1.1)))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="22">
         <f>RANK(E12,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10460,19 +10785,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*('Supuestos'!$C$28*1.1))+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="24">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="22">
         <f>RANK(E13,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10488,19 +10813,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <f>(((((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25)*'Supuestos'!$C$28)+((((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)-((((((IF('Supuestos'!$C$17=1,(IF('Supuestos'!$C$17=1,(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$18,0)),(IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))))*'Supuestos'!$C$21)*'Supuestos'!$C$22)*'Supuestos'!$C$23)*'Supuestos'!$C$24)*'Supuestos'!$C$25))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-('Supuestos'!$C$34*0.9)-'Supuestos'!$C$35))-((IF((IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14=0,0,'Supuestos'!$C$9/1000/('Supuestos'!$C$10*'Supuestos'!$C$11*'Supuestos'!$C$14)))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="22">
         <f>RANK(E14,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10643,51 +10968,51 @@
           <t>Inversión en publicidad del mes</t>
         </is>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <f>'Supuestos'!$C$8*1</f>
         <v/>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <f>C6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <f>D6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <f>E6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <f>F6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <f>G6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="21">
         <f>H6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="21">
         <f>I6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="21">
         <f>J6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="21">
         <f>K6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="21">
         <f>L6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="21">
         <f>M6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
@@ -10702,51 +11027,51 @@
           <t>Leads compradas</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>IF('Modelo'!$C$10=0,0,C6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="22">
         <f>IF('Modelo'!$C$10=0,0,D6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <f>IF('Modelo'!$C$10=0,0,E6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <f>IF('Modelo'!$C$10=0,0,F6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f>IF('Modelo'!$C$10=0,0,G6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f>IF('Modelo'!$C$10=0,0,H6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="22">
         <f>IF('Modelo'!$C$10=0,0,I6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="22">
         <f>IF('Modelo'!$C$10=0,0,J6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="22">
         <f>IF('Modelo'!$C$10=0,0,K6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="22">
         <f>IF('Modelo'!$C$10=0,0,L6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="22">
         <f>IF('Modelo'!$C$10=0,0,M6/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="22">
         <f>IF('Modelo'!$C$10=0,0,N6/'Modelo'!$C$10)</f>
         <v/>
       </c>
@@ -10761,51 +11086,51 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <f>C7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <f>D7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>E7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <f>F7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <f>G7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <f>H7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="26">
         <f>I7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="26">
         <f>J7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="26">
         <f>K7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="26">
         <f>L7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="26">
         <f>M7*'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="26">
         <f>N7*'Modelo'!$C$31</f>
         <v/>
       </c>
@@ -10820,51 +11145,51 @@
           <t>Facturado (todos los productos)</t>
         </is>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <f>C7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>D7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <f>E7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <f>F7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="21">
         <f>G7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="21">
         <f>H7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="21">
         <f>I7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="21">
         <f>J7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="21">
         <f>K7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="21">
         <f>L7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="M9" s="20">
+      <c r="M9" s="21">
         <f>M7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="21">
         <f>N7*'Modelo'!$C$32</f>
         <v/>
       </c>
@@ -10879,51 +11204,51 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <f>C9*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <f>D9*'Supuestos'!$C$40+C9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>E9*'Supuestos'!$C$40+D9*'Supuestos'!$C$41+C9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <f>F9*'Supuestos'!$C$40+E9*'Supuestos'!$C$41+D9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="21">
         <f>G9*'Supuestos'!$C$40+F9*'Supuestos'!$C$41+E9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="21">
         <f>H9*'Supuestos'!$C$40+G9*'Supuestos'!$C$41+F9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="21">
         <f>I9*'Supuestos'!$C$40+H9*'Supuestos'!$C$41+G9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="21">
         <f>J9*'Supuestos'!$C$40+I9*'Supuestos'!$C$41+H9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="21">
         <f>K9*'Supuestos'!$C$40+J9*'Supuestos'!$C$41+I9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="21">
         <f>L9*'Supuestos'!$C$40+K9*'Supuestos'!$C$41+J9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="M10" s="20">
+      <c r="M10" s="21">
         <f>M9*'Supuestos'!$C$40+L9*'Supuestos'!$C$41+K9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="21">
         <f>N9*'Supuestos'!$C$40+M9*'Supuestos'!$C$41+L9*'Supuestos'!$C$42</f>
         <v/>
       </c>
@@ -10938,51 +11263,51 @@
           <t>Comisiones y reembolsos</t>
         </is>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <f>C10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>D10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>E10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <f>F10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="21">
         <f>G10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="21">
         <f>H10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="21">
         <f>I10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="21">
         <f>J10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="21">
         <f>K10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="21">
         <f>L10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="M11" s="20">
+      <c r="M11" s="21">
         <f>M10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="21">
         <f>N10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
@@ -10997,51 +11322,51 @@
           <t>Costos por unidad (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>C7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>D7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>E7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <f>F7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <f>G7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="21">
         <f>H7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="21">
         <f>I7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="21">
         <f>J7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="21">
         <f>K7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="21">
         <f>L7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="M12" s="20">
+      <c r="M12" s="21">
         <f>M7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="21">
         <f>N7*'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -11056,51 +11381,51 @@
           <t>Costos fijos del mes</t>
         </is>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="L13" s="20">
+      <c r="L13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="M13" s="20">
+      <c r="M13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="21">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
@@ -11229,51 +11554,51 @@
           <t>Saldo de caja (caja inicial + ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <f>'Supuestos'!$C$49+C15</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <f>'Supuestos'!$C$49+D15</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>'Supuestos'!$C$49+E15</f>
         <v/>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <f>'Supuestos'!$C$49+F15</f>
         <v/>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <f>'Supuestos'!$C$49+G15</f>
         <v/>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="21">
         <f>'Supuestos'!$C$49+H15</f>
         <v/>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="21">
         <f>'Supuestos'!$C$49+I15</f>
         <v/>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="21">
         <f>'Supuestos'!$C$49+J15</f>
         <v/>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="21">
         <f>'Supuestos'!$C$49+K15</f>
         <v/>
       </c>
-      <c r="L16" s="20">
+      <c r="L16" s="21">
         <f>'Supuestos'!$C$49+L15</f>
         <v/>
       </c>
-      <c r="M16" s="20">
+      <c r="M16" s="21">
         <f>'Supuestos'!$C$49+M15</f>
         <v/>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="21">
         <f>'Supuestos'!$C$49+N15</f>
         <v/>
       </c>
